--- a/public/TagWarningBaiLieu.xlsx
+++ b/public/TagWarningBaiLieu.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7CF259C-80CD-49C3-A881-76D9C9A2959F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D4DB021-5F87-416E-B537-C43D425EE415}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3420" yWindow="3420" windowWidth="21600" windowHeight="11385" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LocBuiC1" sheetId="18" r:id="rId1"/>
@@ -14,18 +14,28 @@
     <sheet name="LocBuiC4" sheetId="22" r:id="rId4"/>
     <sheet name="LocBuiC5" sheetId="20" r:id="rId5"/>
     <sheet name="TrungThe" sheetId="23" r:id="rId6"/>
+    <sheet name="CheBien" sheetId="24" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1306" uniqueCount="567">
   <si>
     <t>Tag0</t>
   </si>
@@ -1289,13 +1299,460 @@
   </si>
   <si>
     <t>null</t>
+  </si>
+  <si>
+    <t>Động cơ chính máy nghiền</t>
+  </si>
+  <si>
+    <t>Nhiệt độ cuộn dây A</t>
+  </si>
+  <si>
+    <t>S7Program/MillDP_AI22.PV_OUT</t>
+  </si>
+  <si>
+    <t>Nhiệt độ cuộn dây B</t>
+  </si>
+  <si>
+    <t>S7Program/MillDP_AI23.PV_OUT</t>
+  </si>
+  <si>
+    <t>Nhiệt độ cuộn dây C</t>
+  </si>
+  <si>
+    <t>S7Program/MillDP_AI24.PV_OUT</t>
+  </si>
+  <si>
+    <t>Nhiệt độ gối trước động cơ</t>
+  </si>
+  <si>
+    <t>S7Program/MillDP_AI25.PV_OUT</t>
+  </si>
+  <si>
+    <t>Nhiệt độ gối sau động cơ</t>
+  </si>
+  <si>
+    <t>S7Program/MillDP_AI26.PV_OUT</t>
+  </si>
+  <si>
+    <t>S7Program/MillDP_AI27.PV_OUT</t>
+  </si>
+  <si>
+    <t>Phân ly</t>
+  </si>
+  <si>
+    <t>S7Program/MillDP_AI14.PV_OUT</t>
+  </si>
+  <si>
+    <t>S7Program/MillDP_AI15.PV_OUT</t>
+  </si>
+  <si>
+    <t>S7Program/MillDP_AI16.PV_OUT</t>
+  </si>
+  <si>
+    <t>Nhiệt độ trục trước động cơ</t>
+  </si>
+  <si>
+    <t>S7Program/MillDP_AI17.PV_OUT</t>
+  </si>
+  <si>
+    <t>Nhiệt độ trục sau động cơ</t>
+  </si>
+  <si>
+    <t>S7Program/MillDP_AI18.PV_OUT</t>
+  </si>
+  <si>
+    <t>Nhiệt độ gối trước phân ly</t>
+  </si>
+  <si>
+    <t>S7Program/MillDP_AI19.PV_OUT</t>
+  </si>
+  <si>
+    <t>Nhiệt độ gối sau phân ly</t>
+  </si>
+  <si>
+    <t>S7Program/MillDP_AI20.PV_OUT</t>
+  </si>
+  <si>
+    <t>S7Program/121_SR01_Current.PV_OUT</t>
+  </si>
+  <si>
+    <t>Động cơ lọc bụi chính</t>
+  </si>
+  <si>
+    <t>S7Program/121_FN02M_ST1.PV_OUT</t>
+  </si>
+  <si>
+    <t>S7Program/121_FN02M_ST2.PV_OUT</t>
+  </si>
+  <si>
+    <t>S7Program/121_FN02M_ST3.PV_OUT</t>
+  </si>
+  <si>
+    <t>S7Program/121_FN02M_Dr_T.PV_OUT</t>
+  </si>
+  <si>
+    <t>S7Program/121_FN02M_NDr_T.PV_OUT</t>
+  </si>
+  <si>
+    <t>Nhiệt độ gối  trước quạt</t>
+  </si>
+  <si>
+    <t>S7Program/121_FN02_Dr_T.PV_OUT</t>
+  </si>
+  <si>
+    <t>Nhiệt độ gối sau quạt</t>
+  </si>
+  <si>
+    <t>S7Program/121_FN02_NDr_T.PV_OUT</t>
+  </si>
+  <si>
+    <t>Độ rung trục động cơ trước X</t>
+  </si>
+  <si>
+    <t>S7Program/121_FN02_Dr_HV.PV_OUT</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>mm/s</t>
+    </r>
+  </si>
+  <si>
+    <t>Độ rung trục động cơ trước Y</t>
+  </si>
+  <si>
+    <t>S7Program/121_FN02_Dr_VV.PV_OUT</t>
+  </si>
+  <si>
+    <t>Độ rung trục động cơ sau X</t>
+  </si>
+  <si>
+    <t>S7Program/121_FN02_NDr_HV.PV_OUT</t>
+  </si>
+  <si>
+    <t>Độ rung trục động cơ sau Y</t>
+  </si>
+  <si>
+    <t>S7Program/121_FN02_NDr_VV.PV_OUT</t>
+  </si>
+  <si>
+    <t>S7Program/121_FN02_Current.PV_OUT</t>
+  </si>
+  <si>
+    <t>Độ rung máy nghiền</t>
+  </si>
+  <si>
+    <t>Độ rung thân máy nghiền phương X</t>
+  </si>
+  <si>
+    <t>S7Program/MillDP_AI28.PV_OUT</t>
+  </si>
+  <si>
+    <t>Độ rung trục ngoài HGT
+chính</t>
+  </si>
+  <si>
+    <t>Độ rung thân HGT phương X</t>
+  </si>
+  <si>
+    <t>S7Program/MillDP_AI29.PV_OUT</t>
+  </si>
+  <si>
+    <t>Độ rung trục bánh răng bên trong HGT chính</t>
+  </si>
+  <si>
+    <t>Độ rung trục bánh răng phương X</t>
+  </si>
+  <si>
+    <t>Do_rung_HGT</t>
+  </si>
+  <si>
+    <t>Vít tải</t>
+  </si>
+  <si>
+    <t>Trục vít tải trong</t>
+  </si>
+  <si>
+    <t>S7Program/MillDP_AI56.PV_OUT</t>
+  </si>
+  <si>
+    <t>Trục vít tải ngoài</t>
+  </si>
+  <si>
+    <t>S7Program/MillDP_AI57.PV_OUT</t>
+  </si>
+  <si>
+    <t>dongdienvittai</t>
+  </si>
+  <si>
+    <t>Băng tải 111BC-01</t>
+  </si>
+  <si>
+    <t>S7Program/111_BC01_Current.PV_OUT</t>
+  </si>
+  <si>
+    <t>luu_luong_can_BC01</t>
+  </si>
+  <si>
+    <t>Quả lô</t>
+  </si>
+  <si>
+    <t>Ví trí quả lô số 1</t>
+  </si>
+  <si>
+    <t>S7Program/MillDP_AI6.PV_OUT</t>
+  </si>
+  <si>
+    <t>mm</t>
+  </si>
+  <si>
+    <t>Ví trí quả lô số 2</t>
+  </si>
+  <si>
+    <t>S7Program/MillDP_AI7.PV_OUT</t>
+  </si>
+  <si>
+    <t>Ví trí quả lô số 3</t>
+  </si>
+  <si>
+    <t>S7Program/MillDP_AI8.PV_OUT</t>
+  </si>
+  <si>
+    <t>Tốc độ quả lô số 1</t>
+  </si>
+  <si>
+    <t>S7Program/MillDP_AI9.PV_OUT</t>
+  </si>
+  <si>
+    <t>r/min</t>
+  </si>
+  <si>
+    <t>Tốc độ quả lô số 2</t>
+  </si>
+  <si>
+    <t>S7Program/MillDP_AI10.PV_OUT</t>
+  </si>
+  <si>
+    <t>Tốc độ quả lô số 3</t>
+  </si>
+  <si>
+    <t>S7Program/MillDP_AI11.PV_OUT</t>
+  </si>
+  <si>
+    <t>Trạm dầu HGT</t>
+  </si>
+  <si>
+    <t>Áp suất số 1</t>
+  </si>
+  <si>
+    <t>S7Program/MillDP_AI30.PV_OUT</t>
+  </si>
+  <si>
+    <t>bar</t>
+  </si>
+  <si>
+    <t>Áp suất số 2</t>
+  </si>
+  <si>
+    <t>S7Program/MillDP_AI31.PV_OUT</t>
+  </si>
+  <si>
+    <t>Áp suất số 3</t>
+  </si>
+  <si>
+    <t>S7Program/MillDP_AI32.PV_OUT</t>
+  </si>
+  <si>
+    <t>Áp suất số 4</t>
+  </si>
+  <si>
+    <t>S7Program/MillDP_AI33.PV_OUT</t>
+  </si>
+  <si>
+    <t>Áp suất số 5</t>
+  </si>
+  <si>
+    <t>S7Program/MillDP_AI34.PV_OUT</t>
+  </si>
+  <si>
+    <t>Áp suất số 6</t>
+  </si>
+  <si>
+    <t>S7Program/MillDP_AI35.PV_OUT</t>
+  </si>
+  <si>
+    <t>Áp suất số 7</t>
+  </si>
+  <si>
+    <t>S7Program/MillDP_AI36.PV_OUT</t>
+  </si>
+  <si>
+    <t>Áp suất số 8</t>
+  </si>
+  <si>
+    <t>S7Program/MillDP_AI37.PV_OUT</t>
+  </si>
+  <si>
+    <t>Áp suất số 9</t>
+  </si>
+  <si>
+    <t>S7Program/MillDP_AI38.PV_OUT</t>
+  </si>
+  <si>
+    <t>Áp suất số 10</t>
+  </si>
+  <si>
+    <t>S7Program/MillDP_AI39.PV_OUT</t>
+  </si>
+  <si>
+    <t>Áp suất số 11</t>
+  </si>
+  <si>
+    <t>S7Program/MillDP_AI40.PV_OUT</t>
+  </si>
+  <si>
+    <t>Áp suất số 12</t>
+  </si>
+  <si>
+    <t>S7Program/MillDP_AI41.PV_OUT</t>
+  </si>
+  <si>
+    <t>Áp suất số 13</t>
+  </si>
+  <si>
+    <t>S7Program/MillDP_AI42.PV_OUT</t>
+  </si>
+  <si>
+    <t>Áp suất số 14</t>
+  </si>
+  <si>
+    <t>S7Program/MillDP_AI43.PV_OUT</t>
+  </si>
+  <si>
+    <t>Áp suất số 15</t>
+  </si>
+  <si>
+    <t>S7Program/MillDP_AI44.PV_OUT</t>
+  </si>
+  <si>
+    <t>Áp suất số 16</t>
+  </si>
+  <si>
+    <t>S7Program/MillDP_AI45.PV_OUT</t>
+  </si>
+  <si>
+    <t>Nhiêt độ bạc trượt 1</t>
+  </si>
+  <si>
+    <t>S7Program/MillDP_AI46.PV_OUT</t>
+  </si>
+  <si>
+    <t>Nhiêt độ bạc trượt 2</t>
+  </si>
+  <si>
+    <t>S7Program/MillDP_AI47.PV_OUT</t>
+  </si>
+  <si>
+    <t>Nhiêt độ bạc trượt 3</t>
+  </si>
+  <si>
+    <t>S7Program/MillDP_AI48.PV_OUT</t>
+  </si>
+  <si>
+    <t>Nhiêt độ bạc trượt 4</t>
+  </si>
+  <si>
+    <t>S7Program/MillDP_AI49.PV_OUT</t>
+  </si>
+  <si>
+    <t>Nhiệt độ phía trên bồn</t>
+  </si>
+  <si>
+    <t>S7Program/MillDP_AI50.PV_OUT</t>
+  </si>
+  <si>
+    <t>Nhiệt độ trục vào ô bi ngoài</t>
+  </si>
+  <si>
+    <t>S7Program/MillDP_AI51.PV_OUT</t>
+  </si>
+  <si>
+    <t>Nhiệt độ trục vào ô bi trong</t>
+  </si>
+  <si>
+    <t>S7Program/MillDP_AI52.PV_OUT</t>
+  </si>
+  <si>
+    <t>Nhiệt đọ ống dẫn đầu vào</t>
+  </si>
+  <si>
+    <t>S7Program/MillDP_AI53.PV_OUT</t>
+  </si>
+  <si>
+    <t>Nhiệt độ đáy HGT</t>
+  </si>
+  <si>
+    <t>S7Program/MillDP_AI54.PV_OUT</t>
+  </si>
+  <si>
+    <t>Trạm thủy lực nâng hạ quả lô</t>
+  </si>
+  <si>
+    <t>Nhiệt độ dầu</t>
+  </si>
+  <si>
+    <t>S7Program/MillDP_AI2.PV_OUT</t>
+  </si>
+  <si>
+    <t>Áp suất làm việc</t>
+  </si>
+  <si>
+    <t>S7Program/MillDP_AI12.PV_OUT</t>
+  </si>
+  <si>
+    <t>Áp suất hồi về</t>
+  </si>
+  <si>
+    <t>S7Program/MillDP_AI13.PV_OUT</t>
+  </si>
+  <si>
+    <t>Trạm dầu bôi trơn quả lô</t>
+  </si>
+  <si>
+    <t>Nhiệt độ dầu bồn dầu</t>
+  </si>
+  <si>
+    <t>S7Program/MillDP_AI1.PV_OUT</t>
+  </si>
+  <si>
+    <t>Nhiệt độ dầu đầu ra 1</t>
+  </si>
+  <si>
+    <t>S7Program/MillDP_AI3.PV_OUT</t>
+  </si>
+  <si>
+    <t>Nhiệt độ dầu đầu ra 2</t>
+  </si>
+  <si>
+    <t>S7Program/MillDP_AI4.PV_OUT</t>
+  </si>
+  <si>
+    <t>Nhiệt độ dầu đầu ra 3</t>
+  </si>
+  <si>
+    <t>S7Program/MillDP_AI5.PV_OUT</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1370,13 +1827,50 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="13"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="15">
@@ -1569,7 +2063,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1600,6 +2094,25 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1638,18 +2151,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1659,13 +2160,31 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1673,17 +2192,41 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1970,19 +2513,19 @@
   <cols>
     <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="47.28515625" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="17"/>
+      <c r="C1" s="24"/>
       <c r="D1" s="6" t="s">
         <v>0</v>
       </c>
@@ -2000,11 +2543,11 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="14"/>
-      <c r="B2" s="16" t="s">
+      <c r="A2" s="21"/>
+      <c r="B2" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="C2" s="17"/>
+      <c r="C2" s="24"/>
       <c r="D2" s="6" t="s">
         <v>1</v>
       </c>
@@ -2016,11 +2559,11 @@
       <c r="H2" s="3"/>
     </row>
     <row r="3" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="14"/>
-      <c r="B3" s="16" t="s">
+      <c r="A3" s="21"/>
+      <c r="B3" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="C3" s="17"/>
+      <c r="C3" s="24"/>
       <c r="D3" s="6" t="s">
         <v>4</v>
       </c>
@@ -2032,8 +2575,8 @@
       <c r="H3" s="3"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="14"/>
-      <c r="B4" s="18" t="s">
+      <c r="A4" s="21"/>
+      <c r="B4" s="25" t="s">
         <v>95</v>
       </c>
       <c r="C4" s="11" t="s">
@@ -2052,8 +2595,8 @@
       <c r="H4" s="3"/>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="14"/>
-      <c r="B5" s="14"/>
+      <c r="A5" s="21"/>
+      <c r="B5" s="21"/>
       <c r="C5" s="11" t="s">
         <v>97</v>
       </c>
@@ -2070,8 +2613,8 @@
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="14"/>
-      <c r="B6" s="14"/>
+      <c r="A6" s="21"/>
+      <c r="B6" s="21"/>
       <c r="C6" s="11" t="s">
         <v>98</v>
       </c>
@@ -2088,8 +2631,8 @@
       <c r="H6" s="3"/>
     </row>
     <row r="7" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="14"/>
-      <c r="B7" s="15"/>
+      <c r="A7" s="21"/>
+      <c r="B7" s="22"/>
       <c r="C7" s="11" t="s">
         <v>99</v>
       </c>
@@ -2106,11 +2649,11 @@
       <c r="H7" s="3"/>
     </row>
     <row r="8" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="14"/>
-      <c r="B8" s="16" t="s">
+      <c r="A8" s="21"/>
+      <c r="B8" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="C8" s="17"/>
+      <c r="C8" s="24"/>
       <c r="D8" s="6" t="s">
         <v>13</v>
       </c>
@@ -2124,8 +2667,8 @@
       <c r="H8" s="3"/>
     </row>
     <row r="9" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="14"/>
-      <c r="B9" s="18" t="s">
+      <c r="A9" s="21"/>
+      <c r="B9" s="25" t="s">
         <v>101</v>
       </c>
       <c r="C9" s="11" t="s">
@@ -2148,8 +2691,8 @@
       </c>
     </row>
     <row r="10" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="14"/>
-      <c r="B10" s="14"/>
+      <c r="A10" s="21"/>
+      <c r="B10" s="21"/>
       <c r="C10" s="11" t="s">
         <v>103</v>
       </c>
@@ -2170,8 +2713,8 @@
       </c>
     </row>
     <row r="11" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="14"/>
-      <c r="B11" s="14"/>
+      <c r="A11" s="21"/>
+      <c r="B11" s="21"/>
       <c r="C11" s="11" t="s">
         <v>104</v>
       </c>
@@ -2192,8 +2735,8 @@
       </c>
     </row>
     <row r="12" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="14"/>
-      <c r="B12" s="14"/>
+      <c r="A12" s="21"/>
+      <c r="B12" s="21"/>
       <c r="C12" s="5" t="s">
         <v>105</v>
       </c>
@@ -2214,8 +2757,8 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="14"/>
-      <c r="B13" s="14"/>
+      <c r="A13" s="21"/>
+      <c r="B13" s="21"/>
       <c r="C13" s="11" t="s">
         <v>88</v>
       </c>
@@ -2236,8 +2779,8 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="14"/>
-      <c r="B14" s="14"/>
+      <c r="A14" s="21"/>
+      <c r="B14" s="21"/>
       <c r="C14" s="11" t="s">
         <v>89</v>
       </c>
@@ -2258,8 +2801,8 @@
       </c>
     </row>
     <row r="15" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="14"/>
-      <c r="B15" s="15"/>
+      <c r="A15" s="21"/>
+      <c r="B15" s="22"/>
       <c r="C15" s="11" t="s">
         <v>90</v>
       </c>
@@ -2280,11 +2823,11 @@
       </c>
     </row>
     <row r="16" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="14"/>
-      <c r="B16" s="19" t="s">
+      <c r="A16" s="21"/>
+      <c r="B16" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="C16" s="20"/>
+      <c r="C16" s="27"/>
       <c r="D16" s="6" t="s">
         <v>21</v>
       </c>
@@ -2298,8 +2841,8 @@
       <c r="H16" s="1"/>
     </row>
     <row r="17" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="14"/>
-      <c r="B17" s="21" t="s">
+      <c r="A17" s="21"/>
+      <c r="B17" s="28" t="s">
         <v>107</v>
       </c>
       <c r="C17" s="11" t="s">
@@ -2322,8 +2865,8 @@
       </c>
     </row>
     <row r="18" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="14"/>
-      <c r="B18" s="22"/>
+      <c r="A18" s="21"/>
+      <c r="B18" s="29"/>
       <c r="C18" s="11" t="s">
         <v>109</v>
       </c>
@@ -2344,8 +2887,8 @@
       </c>
     </row>
     <row r="19" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="14"/>
-      <c r="B19" s="22"/>
+      <c r="A19" s="21"/>
+      <c r="B19" s="29"/>
       <c r="C19" s="11" t="s">
         <v>110</v>
       </c>
@@ -2366,8 +2909,8 @@
       </c>
     </row>
     <row r="20" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="14"/>
-      <c r="B20" s="23"/>
+      <c r="A20" s="21"/>
+      <c r="B20" s="30"/>
       <c r="C20" s="11" t="s">
         <v>111</v>
       </c>
@@ -2388,11 +2931,11 @@
       </c>
     </row>
     <row r="21" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="15"/>
-      <c r="B21" s="24" t="s">
+      <c r="A21" s="22"/>
+      <c r="B21" s="31" t="s">
         <v>112</v>
       </c>
-      <c r="C21" s="17"/>
+      <c r="C21" s="24"/>
       <c r="D21" s="6" t="s">
         <v>28</v>
       </c>
@@ -2435,13 +2978,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="17"/>
+      <c r="C1" s="24"/>
       <c r="D1" s="6" t="s">
         <v>0</v>
       </c>
@@ -2459,11 +3002,11 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="14"/>
-      <c r="B2" s="16" t="s">
+      <c r="A2" s="21"/>
+      <c r="B2" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="C2" s="17"/>
+      <c r="C2" s="24"/>
       <c r="D2" s="6" t="s">
         <v>1</v>
       </c>
@@ -2475,11 +3018,11 @@
       <c r="H2" s="3"/>
     </row>
     <row r="3" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="14"/>
-      <c r="B3" s="16" t="s">
+      <c r="A3" s="21"/>
+      <c r="B3" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="C3" s="17"/>
+      <c r="C3" s="24"/>
       <c r="D3" s="6" t="s">
         <v>4</v>
       </c>
@@ -2491,8 +3034,8 @@
       <c r="H3" s="3"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="14"/>
-      <c r="B4" s="18" t="s">
+      <c r="A4" s="21"/>
+      <c r="B4" s="25" t="s">
         <v>95</v>
       </c>
       <c r="C4" s="5" t="s">
@@ -2511,8 +3054,8 @@
       <c r="H4" s="3"/>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="14"/>
-      <c r="B5" s="14"/>
+      <c r="A5" s="21"/>
+      <c r="B5" s="21"/>
       <c r="C5" s="5" t="s">
         <v>97</v>
       </c>
@@ -2529,8 +3072,8 @@
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="14"/>
-      <c r="B6" s="14"/>
+      <c r="A6" s="21"/>
+      <c r="B6" s="21"/>
       <c r="C6" s="5" t="s">
         <v>98</v>
       </c>
@@ -2547,8 +3090,8 @@
       <c r="H6" s="3"/>
     </row>
     <row r="7" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="14"/>
-      <c r="B7" s="15"/>
+      <c r="A7" s="21"/>
+      <c r="B7" s="22"/>
       <c r="C7" s="5" t="s">
         <v>99</v>
       </c>
@@ -2565,11 +3108,11 @@
       <c r="H7" s="3"/>
     </row>
     <row r="8" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="14"/>
-      <c r="B8" s="16" t="s">
+      <c r="A8" s="21"/>
+      <c r="B8" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="C8" s="17"/>
+      <c r="C8" s="24"/>
       <c r="D8" s="6" t="s">
         <v>13</v>
       </c>
@@ -2583,8 +3126,8 @@
       <c r="H8" s="3"/>
     </row>
     <row r="9" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="14"/>
-      <c r="B9" s="18" t="s">
+      <c r="A9" s="21"/>
+      <c r="B9" s="25" t="s">
         <v>101</v>
       </c>
       <c r="C9" s="5" t="s">
@@ -2607,8 +3150,8 @@
       </c>
     </row>
     <row r="10" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="14"/>
-      <c r="B10" s="14"/>
+      <c r="A10" s="21"/>
+      <c r="B10" s="21"/>
       <c r="C10" s="5" t="s">
         <v>103</v>
       </c>
@@ -2629,8 +3172,8 @@
       </c>
     </row>
     <row r="11" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="14"/>
-      <c r="B11" s="14"/>
+      <c r="A11" s="21"/>
+      <c r="B11" s="21"/>
       <c r="C11" s="5" t="s">
         <v>104</v>
       </c>
@@ -2651,8 +3194,8 @@
       </c>
     </row>
     <row r="12" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="14"/>
-      <c r="B12" s="14"/>
+      <c r="A12" s="21"/>
+      <c r="B12" s="21"/>
       <c r="C12" s="5" t="s">
         <v>105</v>
       </c>
@@ -2673,8 +3216,8 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="14"/>
-      <c r="B13" s="14"/>
+      <c r="A13" s="21"/>
+      <c r="B13" s="21"/>
       <c r="C13" s="5" t="s">
         <v>88</v>
       </c>
@@ -2695,8 +3238,8 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="14"/>
-      <c r="B14" s="14"/>
+      <c r="A14" s="21"/>
+      <c r="B14" s="21"/>
       <c r="C14" s="5" t="s">
         <v>89</v>
       </c>
@@ -2717,8 +3260,8 @@
       </c>
     </row>
     <row r="15" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="14"/>
-      <c r="B15" s="15"/>
+      <c r="A15" s="21"/>
+      <c r="B15" s="22"/>
       <c r="C15" s="5" t="s">
         <v>90</v>
       </c>
@@ -2739,11 +3282,11 @@
       </c>
     </row>
     <row r="16" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="14"/>
-      <c r="B16" s="19" t="s">
+      <c r="A16" s="21"/>
+      <c r="B16" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="C16" s="20"/>
+      <c r="C16" s="27"/>
       <c r="D16" s="6" t="s">
         <v>21</v>
       </c>
@@ -2757,8 +3300,8 @@
       <c r="H16" s="1"/>
     </row>
     <row r="17" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="14"/>
-      <c r="B17" s="21" t="s">
+      <c r="A17" s="21"/>
+      <c r="B17" s="28" t="s">
         <v>107</v>
       </c>
       <c r="C17" s="5" t="s">
@@ -2781,8 +3324,8 @@
       </c>
     </row>
     <row r="18" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="14"/>
-      <c r="B18" s="22"/>
+      <c r="A18" s="21"/>
+      <c r="B18" s="29"/>
       <c r="C18" s="5" t="s">
         <v>109</v>
       </c>
@@ -2803,8 +3346,8 @@
       </c>
     </row>
     <row r="19" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="14"/>
-      <c r="B19" s="22"/>
+      <c r="A19" s="21"/>
+      <c r="B19" s="29"/>
       <c r="C19" s="5" t="s">
         <v>110</v>
       </c>
@@ -2825,8 +3368,8 @@
       </c>
     </row>
     <row r="20" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="14"/>
-      <c r="B20" s="23"/>
+      <c r="A20" s="21"/>
+      <c r="B20" s="30"/>
       <c r="C20" s="5" t="s">
         <v>111</v>
       </c>
@@ -2847,11 +3390,11 @@
       </c>
     </row>
     <row r="21" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="15"/>
-      <c r="B21" s="19" t="s">
+      <c r="A21" s="22"/>
+      <c r="B21" s="26" t="s">
         <v>112</v>
       </c>
-      <c r="C21" s="17"/>
+      <c r="C21" s="24"/>
       <c r="D21" s="6" t="s">
         <v>28</v>
       </c>
@@ -2893,13 +3436,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="21" t="s">
         <v>158</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="17"/>
+      <c r="C1" s="24"/>
       <c r="D1" s="6" t="s">
         <v>0</v>
       </c>
@@ -2917,11 +3460,11 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="14"/>
-      <c r="B2" s="16" t="s">
+      <c r="A2" s="21"/>
+      <c r="B2" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="C2" s="17"/>
+      <c r="C2" s="24"/>
       <c r="D2" s="6" t="s">
         <v>1</v>
       </c>
@@ -2933,11 +3476,11 @@
       <c r="H2" s="3"/>
     </row>
     <row r="3" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="14"/>
-      <c r="B3" s="16" t="s">
+      <c r="A3" s="21"/>
+      <c r="B3" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="C3" s="17"/>
+      <c r="C3" s="24"/>
       <c r="D3" s="6" t="s">
         <v>4</v>
       </c>
@@ -2949,8 +3492,8 @@
       <c r="H3" s="3"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="14"/>
-      <c r="B4" s="18" t="s">
+      <c r="A4" s="21"/>
+      <c r="B4" s="25" t="s">
         <v>95</v>
       </c>
       <c r="C4" s="5" t="s">
@@ -2969,8 +3512,8 @@
       <c r="H4" s="3"/>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="14"/>
-      <c r="B5" s="14"/>
+      <c r="A5" s="21"/>
+      <c r="B5" s="21"/>
       <c r="C5" s="5" t="s">
         <v>97</v>
       </c>
@@ -2987,8 +3530,8 @@
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="14"/>
-      <c r="B6" s="14"/>
+      <c r="A6" s="21"/>
+      <c r="B6" s="21"/>
       <c r="C6" s="5" t="s">
         <v>98</v>
       </c>
@@ -3005,8 +3548,8 @@
       <c r="H6" s="3"/>
     </row>
     <row r="7" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="14"/>
-      <c r="B7" s="15"/>
+      <c r="A7" s="21"/>
+      <c r="B7" s="22"/>
       <c r="C7" s="5" t="s">
         <v>99</v>
       </c>
@@ -3023,11 +3566,11 @@
       <c r="H7" s="3"/>
     </row>
     <row r="8" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="14"/>
-      <c r="B8" s="16" t="s">
+      <c r="A8" s="21"/>
+      <c r="B8" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="C8" s="17"/>
+      <c r="C8" s="24"/>
       <c r="D8" s="6" t="s">
         <v>13</v>
       </c>
@@ -3041,8 +3584,8 @@
       <c r="H8" s="3"/>
     </row>
     <row r="9" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="14"/>
-      <c r="B9" s="18" t="s">
+      <c r="A9" s="21"/>
+      <c r="B9" s="25" t="s">
         <v>101</v>
       </c>
       <c r="C9" s="5" t="s">
@@ -3065,8 +3608,8 @@
       </c>
     </row>
     <row r="10" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="14"/>
-      <c r="B10" s="14"/>
+      <c r="A10" s="21"/>
+      <c r="B10" s="21"/>
       <c r="C10" s="5" t="s">
         <v>103</v>
       </c>
@@ -3087,8 +3630,8 @@
       </c>
     </row>
     <row r="11" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="14"/>
-      <c r="B11" s="14"/>
+      <c r="A11" s="21"/>
+      <c r="B11" s="21"/>
       <c r="C11" s="5" t="s">
         <v>104</v>
       </c>
@@ -3109,8 +3652,8 @@
       </c>
     </row>
     <row r="12" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="14"/>
-      <c r="B12" s="14"/>
+      <c r="A12" s="21"/>
+      <c r="B12" s="21"/>
       <c r="C12" s="5" t="s">
         <v>105</v>
       </c>
@@ -3131,8 +3674,8 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="14"/>
-      <c r="B13" s="14"/>
+      <c r="A13" s="21"/>
+      <c r="B13" s="21"/>
       <c r="C13" s="5" t="s">
         <v>88</v>
       </c>
@@ -3153,8 +3696,8 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="14"/>
-      <c r="B14" s="14"/>
+      <c r="A14" s="21"/>
+      <c r="B14" s="21"/>
       <c r="C14" s="5" t="s">
         <v>89</v>
       </c>
@@ -3175,8 +3718,8 @@
       </c>
     </row>
     <row r="15" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="14"/>
-      <c r="B15" s="15"/>
+      <c r="A15" s="21"/>
+      <c r="B15" s="22"/>
       <c r="C15" s="5" t="s">
         <v>90</v>
       </c>
@@ -3197,11 +3740,11 @@
       </c>
     </row>
     <row r="16" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="14"/>
-      <c r="B16" s="19" t="s">
+      <c r="A16" s="21"/>
+      <c r="B16" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="C16" s="20"/>
+      <c r="C16" s="27"/>
       <c r="D16" s="6" t="s">
         <v>21</v>
       </c>
@@ -3215,8 +3758,8 @@
       <c r="H16" s="1"/>
     </row>
     <row r="17" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="14"/>
-      <c r="B17" s="21" t="s">
+      <c r="A17" s="21"/>
+      <c r="B17" s="28" t="s">
         <v>107</v>
       </c>
       <c r="C17" s="5" t="s">
@@ -3239,8 +3782,8 @@
       </c>
     </row>
     <row r="18" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="14"/>
-      <c r="B18" s="22"/>
+      <c r="A18" s="21"/>
+      <c r="B18" s="29"/>
       <c r="C18" s="5" t="s">
         <v>109</v>
       </c>
@@ -3261,8 +3804,8 @@
       </c>
     </row>
     <row r="19" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="14"/>
-      <c r="B19" s="22"/>
+      <c r="A19" s="21"/>
+      <c r="B19" s="29"/>
       <c r="C19" s="5" t="s">
         <v>110</v>
       </c>
@@ -3283,8 +3826,8 @@
       </c>
     </row>
     <row r="20" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="14"/>
-      <c r="B20" s="23"/>
+      <c r="A20" s="21"/>
+      <c r="B20" s="30"/>
       <c r="C20" s="5" t="s">
         <v>111</v>
       </c>
@@ -3305,11 +3848,11 @@
       </c>
     </row>
     <row r="21" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="15"/>
-      <c r="B21" s="19" t="s">
+      <c r="A21" s="22"/>
+      <c r="B21" s="26" t="s">
         <v>112</v>
       </c>
-      <c r="C21" s="17"/>
+      <c r="C21" s="24"/>
       <c r="D21" s="6" t="s">
         <v>28</v>
       </c>
@@ -3351,13 +3894,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="21" t="s">
         <v>202</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="17"/>
+      <c r="C1" s="24"/>
       <c r="D1" s="6" t="s">
         <v>0</v>
       </c>
@@ -3375,11 +3918,11 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="14"/>
-      <c r="B2" s="16" t="s">
+      <c r="A2" s="21"/>
+      <c r="B2" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="C2" s="17"/>
+      <c r="C2" s="24"/>
       <c r="D2" s="6" t="s">
         <v>1</v>
       </c>
@@ -3391,11 +3934,11 @@
       <c r="H2" s="3"/>
     </row>
     <row r="3" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="14"/>
-      <c r="B3" s="16" t="s">
+      <c r="A3" s="21"/>
+      <c r="B3" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="C3" s="17"/>
+      <c r="C3" s="24"/>
       <c r="D3" s="6" t="s">
         <v>4</v>
       </c>
@@ -3407,8 +3950,8 @@
       <c r="H3" s="3"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="14"/>
-      <c r="B4" s="18" t="s">
+      <c r="A4" s="21"/>
+      <c r="B4" s="25" t="s">
         <v>95</v>
       </c>
       <c r="C4" s="5" t="s">
@@ -3427,8 +3970,8 @@
       <c r="H4" s="3"/>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="14"/>
-      <c r="B5" s="14"/>
+      <c r="A5" s="21"/>
+      <c r="B5" s="21"/>
       <c r="C5" s="5" t="s">
         <v>97</v>
       </c>
@@ -3445,8 +3988,8 @@
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="14"/>
-      <c r="B6" s="14"/>
+      <c r="A6" s="21"/>
+      <c r="B6" s="21"/>
       <c r="C6" s="5" t="s">
         <v>98</v>
       </c>
@@ -3463,8 +4006,8 @@
       <c r="H6" s="3"/>
     </row>
     <row r="7" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="14"/>
-      <c r="B7" s="15"/>
+      <c r="A7" s="21"/>
+      <c r="B7" s="22"/>
       <c r="C7" s="5" t="s">
         <v>99</v>
       </c>
@@ -3481,11 +4024,11 @@
       <c r="H7" s="3"/>
     </row>
     <row r="8" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="14"/>
-      <c r="B8" s="16" t="s">
+      <c r="A8" s="21"/>
+      <c r="B8" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="C8" s="17"/>
+      <c r="C8" s="24"/>
       <c r="D8" s="6" t="s">
         <v>13</v>
       </c>
@@ -3499,8 +4042,8 @@
       <c r="H8" s="3"/>
     </row>
     <row r="9" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="14"/>
-      <c r="B9" s="18" t="s">
+      <c r="A9" s="21"/>
+      <c r="B9" s="25" t="s">
         <v>101</v>
       </c>
       <c r="C9" s="5" t="s">
@@ -3523,8 +4066,8 @@
       </c>
     </row>
     <row r="10" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="14"/>
-      <c r="B10" s="14"/>
+      <c r="A10" s="21"/>
+      <c r="B10" s="21"/>
       <c r="C10" s="5" t="s">
         <v>103</v>
       </c>
@@ -3545,8 +4088,8 @@
       </c>
     </row>
     <row r="11" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="14"/>
-      <c r="B11" s="14"/>
+      <c r="A11" s="21"/>
+      <c r="B11" s="21"/>
       <c r="C11" s="5" t="s">
         <v>104</v>
       </c>
@@ -3567,8 +4110,8 @@
       </c>
     </row>
     <row r="12" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="14"/>
-      <c r="B12" s="14"/>
+      <c r="A12" s="21"/>
+      <c r="B12" s="21"/>
       <c r="C12" s="5" t="s">
         <v>105</v>
       </c>
@@ -3589,8 +4132,8 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="14"/>
-      <c r="B13" s="14"/>
+      <c r="A13" s="21"/>
+      <c r="B13" s="21"/>
       <c r="C13" s="5" t="s">
         <v>88</v>
       </c>
@@ -3611,8 +4154,8 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="14"/>
-      <c r="B14" s="14"/>
+      <c r="A14" s="21"/>
+      <c r="B14" s="21"/>
       <c r="C14" s="5" t="s">
         <v>89</v>
       </c>
@@ -3633,8 +4176,8 @@
       </c>
     </row>
     <row r="15" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="14"/>
-      <c r="B15" s="15"/>
+      <c r="A15" s="21"/>
+      <c r="B15" s="22"/>
       <c r="C15" s="5" t="s">
         <v>90</v>
       </c>
@@ -3655,11 +4198,11 @@
       </c>
     </row>
     <row r="16" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="14"/>
-      <c r="B16" s="19" t="s">
+      <c r="A16" s="21"/>
+      <c r="B16" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="C16" s="20"/>
+      <c r="C16" s="27"/>
       <c r="D16" s="6" t="s">
         <v>21</v>
       </c>
@@ -3673,8 +4216,8 @@
       <c r="H16" s="1"/>
     </row>
     <row r="17" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="14"/>
-      <c r="B17" s="21" t="s">
+      <c r="A17" s="21"/>
+      <c r="B17" s="28" t="s">
         <v>107</v>
       </c>
       <c r="C17" s="5" t="s">
@@ -3697,8 +4240,8 @@
       </c>
     </row>
     <row r="18" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="14"/>
-      <c r="B18" s="22"/>
+      <c r="A18" s="21"/>
+      <c r="B18" s="29"/>
       <c r="C18" s="5" t="s">
         <v>109</v>
       </c>
@@ -3719,8 +4262,8 @@
       </c>
     </row>
     <row r="19" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="14"/>
-      <c r="B19" s="22"/>
+      <c r="A19" s="21"/>
+      <c r="B19" s="29"/>
       <c r="C19" s="5" t="s">
         <v>110</v>
       </c>
@@ -3741,8 +4284,8 @@
       </c>
     </row>
     <row r="20" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="14"/>
-      <c r="B20" s="23"/>
+      <c r="A20" s="21"/>
+      <c r="B20" s="30"/>
       <c r="C20" s="5" t="s">
         <v>111</v>
       </c>
@@ -3763,11 +4306,11 @@
       </c>
     </row>
     <row r="21" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="15"/>
-      <c r="B21" s="19" t="s">
+      <c r="A21" s="22"/>
+      <c r="B21" s="26" t="s">
         <v>112</v>
       </c>
-      <c r="C21" s="17"/>
+      <c r="C21" s="24"/>
       <c r="D21" s="6" t="s">
         <v>28</v>
       </c>
@@ -3808,13 +4351,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="21" t="s">
         <v>201</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="17"/>
+      <c r="C1" s="24"/>
       <c r="D1" s="6" t="s">
         <v>0</v>
       </c>
@@ -3832,11 +4375,11 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="14"/>
-      <c r="B2" s="16" t="s">
+      <c r="A2" s="21"/>
+      <c r="B2" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="C2" s="17"/>
+      <c r="C2" s="24"/>
       <c r="D2" s="6" t="s">
         <v>1</v>
       </c>
@@ -3848,11 +4391,11 @@
       <c r="H2" s="3"/>
     </row>
     <row r="3" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="14"/>
-      <c r="B3" s="16" t="s">
+      <c r="A3" s="21"/>
+      <c r="B3" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="C3" s="17"/>
+      <c r="C3" s="24"/>
       <c r="D3" s="6" t="s">
         <v>4</v>
       </c>
@@ -3864,8 +4407,8 @@
       <c r="H3" s="3"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="14"/>
-      <c r="B4" s="18" t="s">
+      <c r="A4" s="21"/>
+      <c r="B4" s="25" t="s">
         <v>95</v>
       </c>
       <c r="C4" s="5" t="s">
@@ -3884,8 +4427,8 @@
       <c r="H4" s="3"/>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="14"/>
-      <c r="B5" s="14"/>
+      <c r="A5" s="21"/>
+      <c r="B5" s="21"/>
       <c r="C5" s="5" t="s">
         <v>97</v>
       </c>
@@ -3902,8 +4445,8 @@
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="14"/>
-      <c r="B6" s="14"/>
+      <c r="A6" s="21"/>
+      <c r="B6" s="21"/>
       <c r="C6" s="5" t="s">
         <v>98</v>
       </c>
@@ -3920,8 +4463,8 @@
       <c r="H6" s="3"/>
     </row>
     <row r="7" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="14"/>
-      <c r="B7" s="15"/>
+      <c r="A7" s="21"/>
+      <c r="B7" s="22"/>
       <c r="C7" s="5" t="s">
         <v>99</v>
       </c>
@@ -3938,11 +4481,11 @@
       <c r="H7" s="3"/>
     </row>
     <row r="8" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="14"/>
-      <c r="B8" s="16" t="s">
+      <c r="A8" s="21"/>
+      <c r="B8" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="C8" s="17"/>
+      <c r="C8" s="24"/>
       <c r="D8" s="6" t="s">
         <v>13</v>
       </c>
@@ -3956,8 +4499,8 @@
       <c r="H8" s="3"/>
     </row>
     <row r="9" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="14"/>
-      <c r="B9" s="18" t="s">
+      <c r="A9" s="21"/>
+      <c r="B9" s="25" t="s">
         <v>101</v>
       </c>
       <c r="C9" s="5" t="s">
@@ -3980,8 +4523,8 @@
       </c>
     </row>
     <row r="10" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="14"/>
-      <c r="B10" s="14"/>
+      <c r="A10" s="21"/>
+      <c r="B10" s="21"/>
       <c r="C10" s="5" t="s">
         <v>103</v>
       </c>
@@ -4002,8 +4545,8 @@
       </c>
     </row>
     <row r="11" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="14"/>
-      <c r="B11" s="14"/>
+      <c r="A11" s="21"/>
+      <c r="B11" s="21"/>
       <c r="C11" s="5" t="s">
         <v>104</v>
       </c>
@@ -4024,8 +4567,8 @@
       </c>
     </row>
     <row r="12" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="14"/>
-      <c r="B12" s="14"/>
+      <c r="A12" s="21"/>
+      <c r="B12" s="21"/>
       <c r="C12" s="5" t="s">
         <v>105</v>
       </c>
@@ -4046,8 +4589,8 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="14"/>
-      <c r="B13" s="14"/>
+      <c r="A13" s="21"/>
+      <c r="B13" s="21"/>
       <c r="C13" s="5" t="s">
         <v>88</v>
       </c>
@@ -4068,8 +4611,8 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="14"/>
-      <c r="B14" s="14"/>
+      <c r="A14" s="21"/>
+      <c r="B14" s="21"/>
       <c r="C14" s="5" t="s">
         <v>89</v>
       </c>
@@ -4090,8 +4633,8 @@
       </c>
     </row>
     <row r="15" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="14"/>
-      <c r="B15" s="15"/>
+      <c r="A15" s="21"/>
+      <c r="B15" s="22"/>
       <c r="C15" s="5" t="s">
         <v>90</v>
       </c>
@@ -4112,11 +4655,11 @@
       </c>
     </row>
     <row r="16" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="14"/>
-      <c r="B16" s="19" t="s">
+      <c r="A16" s="21"/>
+      <c r="B16" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="C16" s="20"/>
+      <c r="C16" s="27"/>
       <c r="D16" s="6" t="s">
         <v>21</v>
       </c>
@@ -4130,8 +4673,8 @@
       <c r="H16" s="1"/>
     </row>
     <row r="17" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="14"/>
-      <c r="B17" s="21" t="s">
+      <c r="A17" s="21"/>
+      <c r="B17" s="28" t="s">
         <v>107</v>
       </c>
       <c r="C17" s="5" t="s">
@@ -4154,8 +4697,8 @@
       </c>
     </row>
     <row r="18" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="14"/>
-      <c r="B18" s="22"/>
+      <c r="A18" s="21"/>
+      <c r="B18" s="29"/>
       <c r="C18" s="5" t="s">
         <v>109</v>
       </c>
@@ -4176,8 +4719,8 @@
       </c>
     </row>
     <row r="19" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="14"/>
-      <c r="B19" s="22"/>
+      <c r="A19" s="21"/>
+      <c r="B19" s="29"/>
       <c r="C19" s="5" t="s">
         <v>110</v>
       </c>
@@ -4198,8 +4741,8 @@
       </c>
     </row>
     <row r="20" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="14"/>
-      <c r="B20" s="23"/>
+      <c r="A20" s="21"/>
+      <c r="B20" s="30"/>
       <c r="C20" s="5" t="s">
         <v>111</v>
       </c>
@@ -4220,11 +4763,11 @@
       </c>
     </row>
     <row r="21" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="15"/>
-      <c r="B21" s="19" t="s">
+      <c r="A21" s="22"/>
+      <c r="B21" s="26" t="s">
         <v>112</v>
       </c>
-      <c r="C21" s="17"/>
+      <c r="C21" s="24"/>
       <c r="D21" s="6" t="s">
         <v>28</v>
       </c>
@@ -4267,13 +4810,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="38" t="s">
         <v>347</v>
       </c>
-      <c r="B1" s="29" t="s">
+      <c r="B1" s="32" t="s">
         <v>348</v>
       </c>
-      <c r="C1" s="29" t="s">
+      <c r="C1" s="32" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
@@ -4296,9 +4839,9 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="34"/>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
+      <c r="A2" s="40"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
       <c r="D2" s="2" t="s">
         <v>5</v>
       </c>
@@ -4319,9 +4862,9 @@
       </c>
     </row>
     <row r="3" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="34"/>
-      <c r="B3" s="30"/>
-      <c r="C3" s="31"/>
+      <c r="A3" s="40"/>
+      <c r="B3" s="33"/>
+      <c r="C3" s="34"/>
       <c r="D3" s="2" t="s">
         <v>7</v>
       </c>
@@ -4342,9 +4885,9 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="34"/>
-      <c r="B4" s="30"/>
-      <c r="C4" s="25" t="s">
+      <c r="A4" s="40"/>
+      <c r="B4" s="33"/>
+      <c r="C4" s="38" t="s">
         <v>349</v>
       </c>
       <c r="D4" s="2" t="s">
@@ -4367,9 +4910,9 @@
       </c>
     </row>
     <row r="5" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="34"/>
-      <c r="B5" s="31"/>
-      <c r="C5" s="26"/>
+      <c r="A5" s="40"/>
+      <c r="B5" s="34"/>
+      <c r="C5" s="39"/>
       <c r="D5" s="10" t="s">
         <v>11</v>
       </c>
@@ -4390,12 +4933,12 @@
       </c>
     </row>
     <row r="6" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="26"/>
-      <c r="B6" s="32" t="s">
+      <c r="A6" s="39"/>
+      <c r="B6" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="38"/>
-      <c r="D6" s="33"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="43"/>
       <c r="E6" s="9" t="s">
         <v>10</v>
       </c>
@@ -4405,21 +4948,21 @@
       <c r="G6" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="H6" s="39">
+      <c r="H6" s="13">
         <v>110</v>
       </c>
-      <c r="I6" s="40">
+      <c r="I6" s="14">
         <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="29" t="s">
+      <c r="A7" s="32" t="s">
         <v>350</v>
       </c>
-      <c r="B7" s="29" t="s">
+      <c r="B7" s="32" t="s">
         <v>348</v>
       </c>
-      <c r="C7" s="29" t="s">
+      <c r="C7" s="32" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2" t="s">
@@ -4442,9 +4985,9 @@
       </c>
     </row>
     <row r="8" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="30"/>
-      <c r="B8" s="30"/>
-      <c r="C8" s="30"/>
+      <c r="A8" s="33"/>
+      <c r="B8" s="33"/>
+      <c r="C8" s="33"/>
       <c r="D8" s="2" t="s">
         <v>5</v>
       </c>
@@ -4465,9 +5008,9 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="30"/>
-      <c r="B9" s="30"/>
-      <c r="C9" s="31"/>
+      <c r="A9" s="33"/>
+      <c r="B9" s="33"/>
+      <c r="C9" s="34"/>
       <c r="D9" s="2" t="s">
         <v>7</v>
       </c>
@@ -4488,9 +5031,9 @@
       </c>
     </row>
     <row r="10" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="30"/>
-      <c r="B10" s="30"/>
-      <c r="C10" s="25" t="s">
+      <c r="A10" s="33"/>
+      <c r="B10" s="33"/>
+      <c r="C10" s="38" t="s">
         <v>349</v>
       </c>
       <c r="D10" s="2" t="s">
@@ -4513,9 +5056,9 @@
       </c>
     </row>
     <row r="11" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="30"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="26"/>
+      <c r="A11" s="33"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="39"/>
       <c r="D11" s="2" t="s">
         <v>11</v>
       </c>
@@ -4536,12 +5079,12 @@
       </c>
     </row>
     <row r="12" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="31"/>
-      <c r="B12" s="27" t="s">
+      <c r="A12" s="34"/>
+      <c r="B12" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="37"/>
-      <c r="D12" s="28"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="37"/>
       <c r="E12" s="9" t="s">
         <v>17</v>
       </c>
@@ -4551,21 +5094,21 @@
       <c r="G12" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="H12" s="39">
+      <c r="H12" s="13">
         <v>8</v>
       </c>
-      <c r="I12" s="40">
+      <c r="I12" s="14">
         <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="25" t="s">
+      <c r="A13" s="38" t="s">
         <v>351</v>
       </c>
-      <c r="B13" s="29" t="s">
+      <c r="B13" s="32" t="s">
         <v>348</v>
       </c>
-      <c r="C13" s="29" t="s">
+      <c r="C13" s="32" t="s">
         <v>2</v>
       </c>
       <c r="D13" s="2" t="s">
@@ -4588,9 +5131,9 @@
       </c>
     </row>
     <row r="14" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="34"/>
-      <c r="B14" s="30"/>
-      <c r="C14" s="30"/>
+      <c r="A14" s="40"/>
+      <c r="B14" s="33"/>
+      <c r="C14" s="33"/>
       <c r="D14" s="2" t="s">
         <v>5</v>
       </c>
@@ -4611,9 +5154,9 @@
       </c>
     </row>
     <row r="15" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="34"/>
-      <c r="B15" s="30"/>
-      <c r="C15" s="31"/>
+      <c r="A15" s="40"/>
+      <c r="B15" s="33"/>
+      <c r="C15" s="34"/>
       <c r="D15" s="2" t="s">
         <v>7</v>
       </c>
@@ -4634,9 +5177,9 @@
       </c>
     </row>
     <row r="16" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="34"/>
-      <c r="B16" s="30"/>
-      <c r="C16" s="25" t="s">
+      <c r="A16" s="40"/>
+      <c r="B16" s="33"/>
+      <c r="C16" s="38" t="s">
         <v>349</v>
       </c>
       <c r="D16" s="2" t="s">
@@ -4659,9 +5202,9 @@
       </c>
     </row>
     <row r="17" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="34"/>
-      <c r="B17" s="31"/>
-      <c r="C17" s="26"/>
+      <c r="A17" s="40"/>
+      <c r="B17" s="34"/>
+      <c r="C17" s="39"/>
       <c r="D17" s="2" t="s">
         <v>11</v>
       </c>
@@ -4682,12 +5225,12 @@
       </c>
     </row>
     <row r="18" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="34"/>
-      <c r="B18" s="27" t="s">
+      <c r="A18" s="40"/>
+      <c r="B18" s="35" t="s">
         <v>352</v>
       </c>
-      <c r="C18" s="37"/>
-      <c r="D18" s="28"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="37"/>
       <c r="E18" s="9" t="s">
         <v>25</v>
       </c>
@@ -4697,20 +5240,20 @@
       <c r="G18" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="H18" s="39">
+      <c r="H18" s="13">
         <v>8</v>
       </c>
-      <c r="I18" s="40">
+      <c r="I18" s="14">
         <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="26"/>
-      <c r="B19" s="27" t="s">
+      <c r="A19" s="39"/>
+      <c r="B19" s="35" t="s">
         <v>353</v>
       </c>
-      <c r="C19" s="37"/>
-      <c r="D19" s="28"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="37"/>
       <c r="E19" s="9" t="s">
         <v>26</v>
       </c>
@@ -4720,21 +5263,21 @@
       <c r="G19" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="H19" s="39">
+      <c r="H19" s="13">
         <v>8</v>
       </c>
-      <c r="I19" s="40">
+      <c r="I19" s="14">
         <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="25" t="s">
+      <c r="A20" s="38" t="s">
         <v>354</v>
       </c>
-      <c r="B20" s="29" t="s">
+      <c r="B20" s="32" t="s">
         <v>348</v>
       </c>
-      <c r="C20" s="29" t="s">
+      <c r="C20" s="32" t="s">
         <v>2</v>
       </c>
       <c r="D20" s="2" t="s">
@@ -4757,9 +5300,9 @@
       </c>
     </row>
     <row r="21" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="34"/>
-      <c r="B21" s="30"/>
-      <c r="C21" s="30"/>
+      <c r="A21" s="40"/>
+      <c r="B21" s="33"/>
+      <c r="C21" s="33"/>
       <c r="D21" s="2" t="s">
         <v>5</v>
       </c>
@@ -4780,9 +5323,9 @@
       </c>
     </row>
     <row r="22" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="34"/>
-      <c r="B22" s="30"/>
-      <c r="C22" s="31"/>
+      <c r="A22" s="40"/>
+      <c r="B22" s="33"/>
+      <c r="C22" s="34"/>
       <c r="D22" s="2" t="s">
         <v>7</v>
       </c>
@@ -4803,9 +5346,9 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="34"/>
-      <c r="B23" s="30"/>
-      <c r="C23" s="25" t="s">
+      <c r="A23" s="40"/>
+      <c r="B23" s="33"/>
+      <c r="C23" s="38" t="s">
         <v>349</v>
       </c>
       <c r="D23" s="2" t="s">
@@ -4828,9 +5371,9 @@
       </c>
     </row>
     <row r="24" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="34"/>
-      <c r="B24" s="31"/>
-      <c r="C24" s="26"/>
+      <c r="A24" s="40"/>
+      <c r="B24" s="34"/>
+      <c r="C24" s="39"/>
       <c r="D24" s="2" t="s">
         <v>11</v>
       </c>
@@ -4851,12 +5394,12 @@
       </c>
     </row>
     <row r="25" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="34"/>
-      <c r="B25" s="27" t="s">
+      <c r="A25" s="40"/>
+      <c r="B25" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="37"/>
-      <c r="D25" s="28"/>
+      <c r="C25" s="36"/>
+      <c r="D25" s="37"/>
       <c r="E25" s="9" t="s">
         <v>33</v>
       </c>
@@ -4866,20 +5409,20 @@
       <c r="G25" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="H25" s="39">
+      <c r="H25" s="13">
         <v>8</v>
       </c>
-      <c r="I25" s="40">
+      <c r="I25" s="14">
         <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A26" s="26"/>
-      <c r="B26" s="27" t="s">
+      <c r="A26" s="39"/>
+      <c r="B26" s="35" t="s">
         <v>355</v>
       </c>
-      <c r="C26" s="37"/>
-      <c r="D26" s="28"/>
+      <c r="C26" s="36"/>
+      <c r="D26" s="37"/>
       <c r="E26" s="9" t="s">
         <v>34</v>
       </c>
@@ -4889,21 +5432,21 @@
       <c r="G26" s="3" t="s">
         <v>419</v>
       </c>
-      <c r="H26" s="39">
+      <c r="H26" s="13">
         <v>8</v>
       </c>
-      <c r="I26" s="40">
+      <c r="I26" s="14">
         <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A27" s="35" t="s">
+      <c r="A27" s="44" t="s">
         <v>356</v>
       </c>
-      <c r="B27" s="29" t="s">
+      <c r="B27" s="32" t="s">
         <v>348</v>
       </c>
-      <c r="C27" s="29" t="s">
+      <c r="C27" s="32" t="s">
         <v>2</v>
       </c>
       <c r="D27" s="2" t="s">
@@ -4926,9 +5469,9 @@
       </c>
     </row>
     <row r="28" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A28" s="34"/>
-      <c r="B28" s="30"/>
-      <c r="C28" s="30"/>
+      <c r="A28" s="40"/>
+      <c r="B28" s="33"/>
+      <c r="C28" s="33"/>
       <c r="D28" s="2" t="s">
         <v>5</v>
       </c>
@@ -4949,9 +5492,9 @@
       </c>
     </row>
     <row r="29" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A29" s="34"/>
-      <c r="B29" s="30"/>
-      <c r="C29" s="31"/>
+      <c r="A29" s="40"/>
+      <c r="B29" s="33"/>
+      <c r="C29" s="34"/>
       <c r="D29" s="2" t="s">
         <v>7</v>
       </c>
@@ -4972,9 +5515,9 @@
       </c>
     </row>
     <row r="30" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A30" s="34"/>
-      <c r="B30" s="30"/>
-      <c r="C30" s="25" t="s">
+      <c r="A30" s="40"/>
+      <c r="B30" s="33"/>
+      <c r="C30" s="38" t="s">
         <v>349</v>
       </c>
       <c r="D30" s="2" t="s">
@@ -4997,9 +5540,9 @@
       </c>
     </row>
     <row r="31" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A31" s="34"/>
-      <c r="B31" s="31"/>
-      <c r="C31" s="26"/>
+      <c r="A31" s="40"/>
+      <c r="B31" s="34"/>
+      <c r="C31" s="39"/>
       <c r="D31" s="2" t="s">
         <v>11</v>
       </c>
@@ -5020,12 +5563,12 @@
       </c>
     </row>
     <row r="32" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A32" s="26"/>
-      <c r="B32" s="27" t="s">
+      <c r="A32" s="39"/>
+      <c r="B32" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="C32" s="37"/>
-      <c r="D32" s="28"/>
+      <c r="C32" s="36"/>
+      <c r="D32" s="37"/>
       <c r="E32" s="9" t="s">
         <v>40</v>
       </c>
@@ -5035,21 +5578,21 @@
       <c r="G32" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="H32" s="39">
+      <c r="H32" s="13">
         <v>8</v>
       </c>
-      <c r="I32" s="40">
+      <c r="I32" s="14">
         <v>11</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A33" s="25" t="s">
+      <c r="A33" s="38" t="s">
         <v>357</v>
       </c>
-      <c r="B33" s="29" t="s">
+      <c r="B33" s="32" t="s">
         <v>348</v>
       </c>
-      <c r="C33" s="29" t="s">
+      <c r="C33" s="32" t="s">
         <v>2</v>
       </c>
       <c r="D33" s="2" t="s">
@@ -5072,9 +5615,9 @@
       </c>
     </row>
     <row r="34" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A34" s="34"/>
-      <c r="B34" s="30"/>
-      <c r="C34" s="30"/>
+      <c r="A34" s="40"/>
+      <c r="B34" s="33"/>
+      <c r="C34" s="33"/>
       <c r="D34" s="2" t="s">
         <v>5</v>
       </c>
@@ -5095,9 +5638,9 @@
       </c>
     </row>
     <row r="35" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A35" s="34"/>
-      <c r="B35" s="30"/>
-      <c r="C35" s="31"/>
+      <c r="A35" s="40"/>
+      <c r="B35" s="33"/>
+      <c r="C35" s="34"/>
       <c r="D35" s="2" t="s">
         <v>7</v>
       </c>
@@ -5118,9 +5661,9 @@
       </c>
     </row>
     <row r="36" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A36" s="34"/>
-      <c r="B36" s="30"/>
-      <c r="C36" s="25" t="s">
+      <c r="A36" s="40"/>
+      <c r="B36" s="33"/>
+      <c r="C36" s="38" t="s">
         <v>349</v>
       </c>
       <c r="D36" s="2" t="s">
@@ -5143,9 +5686,9 @@
       </c>
     </row>
     <row r="37" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A37" s="34"/>
-      <c r="B37" s="31"/>
-      <c r="C37" s="26"/>
+      <c r="A37" s="40"/>
+      <c r="B37" s="34"/>
+      <c r="C37" s="39"/>
       <c r="D37" s="2" t="s">
         <v>11</v>
       </c>
@@ -5166,12 +5709,12 @@
       </c>
     </row>
     <row r="38" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A38" s="26"/>
-      <c r="B38" s="27" t="s">
+      <c r="A38" s="39"/>
+      <c r="B38" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="C38" s="37"/>
-      <c r="D38" s="28"/>
+      <c r="C38" s="36"/>
+      <c r="D38" s="37"/>
       <c r="E38" s="9" t="s">
         <v>46</v>
       </c>
@@ -5181,21 +5724,21 @@
       <c r="G38" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="H38" s="39">
+      <c r="H38" s="13">
         <v>8</v>
       </c>
-      <c r="I38" s="40">
+      <c r="I38" s="14">
         <v>11</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A39" s="25" t="s">
+      <c r="A39" s="38" t="s">
         <v>358</v>
       </c>
-      <c r="B39" s="29" t="s">
+      <c r="B39" s="32" t="s">
         <v>348</v>
       </c>
-      <c r="C39" s="29" t="s">
+      <c r="C39" s="32" t="s">
         <v>2</v>
       </c>
       <c r="D39" s="2" t="s">
@@ -5218,9 +5761,9 @@
       </c>
     </row>
     <row r="40" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A40" s="34"/>
-      <c r="B40" s="30"/>
-      <c r="C40" s="30"/>
+      <c r="A40" s="40"/>
+      <c r="B40" s="33"/>
+      <c r="C40" s="33"/>
       <c r="D40" s="2" t="s">
         <v>5</v>
       </c>
@@ -5241,9 +5784,9 @@
       </c>
     </row>
     <row r="41" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A41" s="34"/>
-      <c r="B41" s="30"/>
-      <c r="C41" s="31"/>
+      <c r="A41" s="40"/>
+      <c r="B41" s="33"/>
+      <c r="C41" s="34"/>
       <c r="D41" s="2" t="s">
         <v>7</v>
       </c>
@@ -5264,9 +5807,9 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A42" s="34"/>
-      <c r="B42" s="30"/>
-      <c r="C42" s="25" t="s">
+      <c r="A42" s="40"/>
+      <c r="B42" s="33"/>
+      <c r="C42" s="38" t="s">
         <v>349</v>
       </c>
       <c r="D42" s="2" t="s">
@@ -5289,9 +5832,9 @@
       </c>
     </row>
     <row r="43" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A43" s="34"/>
-      <c r="B43" s="31"/>
-      <c r="C43" s="26"/>
+      <c r="A43" s="40"/>
+      <c r="B43" s="34"/>
+      <c r="C43" s="39"/>
       <c r="D43" s="2" t="s">
         <v>11</v>
       </c>
@@ -5312,12 +5855,12 @@
       </c>
     </row>
     <row r="44" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A44" s="26"/>
-      <c r="B44" s="27" t="s">
+      <c r="A44" s="39"/>
+      <c r="B44" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="C44" s="37"/>
-      <c r="D44" s="28"/>
+      <c r="C44" s="36"/>
+      <c r="D44" s="37"/>
       <c r="E44" s="9" t="s">
         <v>52</v>
       </c>
@@ -5327,21 +5870,21 @@
       <c r="G44" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="H44" s="39">
+      <c r="H44" s="13">
         <v>8</v>
       </c>
-      <c r="I44" s="40">
+      <c r="I44" s="14">
         <v>11</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A45" s="25" t="s">
+      <c r="A45" s="38" t="s">
         <v>359</v>
       </c>
-      <c r="B45" s="29" t="s">
+      <c r="B45" s="32" t="s">
         <v>348</v>
       </c>
-      <c r="C45" s="29" t="s">
+      <c r="C45" s="32" t="s">
         <v>2</v>
       </c>
       <c r="D45" s="2" t="s">
@@ -5364,9 +5907,9 @@
       </c>
     </row>
     <row r="46" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A46" s="34"/>
-      <c r="B46" s="30"/>
-      <c r="C46" s="30"/>
+      <c r="A46" s="40"/>
+      <c r="B46" s="33"/>
+      <c r="C46" s="33"/>
       <c r="D46" s="2" t="s">
         <v>5</v>
       </c>
@@ -5387,9 +5930,9 @@
       </c>
     </row>
     <row r="47" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A47" s="34"/>
-      <c r="B47" s="30"/>
-      <c r="C47" s="31"/>
+      <c r="A47" s="40"/>
+      <c r="B47" s="33"/>
+      <c r="C47" s="34"/>
       <c r="D47" s="2" t="s">
         <v>7</v>
       </c>
@@ -5410,9 +5953,9 @@
       </c>
     </row>
     <row r="48" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A48" s="34"/>
-      <c r="B48" s="30"/>
-      <c r="C48" s="25" t="s">
+      <c r="A48" s="40"/>
+      <c r="B48" s="33"/>
+      <c r="C48" s="38" t="s">
         <v>349</v>
       </c>
       <c r="D48" s="2" t="s">
@@ -5435,9 +5978,9 @@
       </c>
     </row>
     <row r="49" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A49" s="34"/>
-      <c r="B49" s="31"/>
-      <c r="C49" s="26"/>
+      <c r="A49" s="40"/>
+      <c r="B49" s="34"/>
+      <c r="C49" s="39"/>
       <c r="D49" s="2" t="s">
         <v>11</v>
       </c>
@@ -5458,12 +6001,12 @@
       </c>
     </row>
     <row r="50" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A50" s="26"/>
-      <c r="B50" s="27" t="s">
+      <c r="A50" s="39"/>
+      <c r="B50" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="C50" s="37"/>
-      <c r="D50" s="28"/>
+      <c r="C50" s="36"/>
+      <c r="D50" s="37"/>
       <c r="E50" s="9" t="s">
         <v>58</v>
       </c>
@@ -5473,21 +6016,21 @@
       <c r="G50" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="H50" s="39">
+      <c r="H50" s="13">
         <v>8</v>
       </c>
-      <c r="I50" s="40">
+      <c r="I50" s="14">
         <v>11</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A51" s="25" t="s">
+      <c r="A51" s="38" t="s">
         <v>360</v>
       </c>
-      <c r="B51" s="29" t="s">
+      <c r="B51" s="32" t="s">
         <v>348</v>
       </c>
-      <c r="C51" s="29" t="s">
+      <c r="C51" s="32" t="s">
         <v>2</v>
       </c>
       <c r="D51" s="2" t="s">
@@ -5510,9 +6053,9 @@
       </c>
     </row>
     <row r="52" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A52" s="34"/>
-      <c r="B52" s="30"/>
-      <c r="C52" s="30"/>
+      <c r="A52" s="40"/>
+      <c r="B52" s="33"/>
+      <c r="C52" s="33"/>
       <c r="D52" s="2" t="s">
         <v>5</v>
       </c>
@@ -5533,9 +6076,9 @@
       </c>
     </row>
     <row r="53" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A53" s="34"/>
-      <c r="B53" s="30"/>
-      <c r="C53" s="31"/>
+      <c r="A53" s="40"/>
+      <c r="B53" s="33"/>
+      <c r="C53" s="34"/>
       <c r="D53" s="2" t="s">
         <v>7</v>
       </c>
@@ -5556,9 +6099,9 @@
       </c>
     </row>
     <row r="54" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A54" s="34"/>
-      <c r="B54" s="30"/>
-      <c r="C54" s="25" t="s">
+      <c r="A54" s="40"/>
+      <c r="B54" s="33"/>
+      <c r="C54" s="38" t="s">
         <v>349</v>
       </c>
       <c r="D54" s="2" t="s">
@@ -5581,9 +6124,9 @@
       </c>
     </row>
     <row r="55" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A55" s="34"/>
-      <c r="B55" s="31"/>
-      <c r="C55" s="26"/>
+      <c r="A55" s="40"/>
+      <c r="B55" s="34"/>
+      <c r="C55" s="39"/>
       <c r="D55" s="2" t="s">
         <v>11</v>
       </c>
@@ -5604,12 +6147,12 @@
       </c>
     </row>
     <row r="56" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A56" s="26"/>
-      <c r="B56" s="27" t="s">
+      <c r="A56" s="39"/>
+      <c r="B56" s="35" t="s">
         <v>355</v>
       </c>
-      <c r="C56" s="37"/>
-      <c r="D56" s="28"/>
+      <c r="C56" s="36"/>
+      <c r="D56" s="37"/>
       <c r="E56" s="9" t="s">
         <v>64</v>
       </c>
@@ -5619,21 +6162,21 @@
       <c r="G56" s="3" t="s">
         <v>419</v>
       </c>
-      <c r="H56" s="39">
+      <c r="H56" s="13">
         <v>8</v>
       </c>
-      <c r="I56" s="40">
+      <c r="I56" s="14">
         <v>11</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A57" s="36" t="s">
+      <c r="A57" s="45" t="s">
         <v>361</v>
       </c>
-      <c r="B57" s="29" t="s">
+      <c r="B57" s="32" t="s">
         <v>348</v>
       </c>
-      <c r="C57" s="29" t="s">
+      <c r="C57" s="32" t="s">
         <v>2</v>
       </c>
       <c r="D57" s="2" t="s">
@@ -5656,9 +6199,9 @@
       </c>
     </row>
     <row r="58" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A58" s="34"/>
-      <c r="B58" s="30"/>
-      <c r="C58" s="30"/>
+      <c r="A58" s="40"/>
+      <c r="B58" s="33"/>
+      <c r="C58" s="33"/>
       <c r="D58" s="2" t="s">
         <v>5</v>
       </c>
@@ -5679,9 +6222,9 @@
       </c>
     </row>
     <row r="59" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A59" s="34"/>
-      <c r="B59" s="30"/>
-      <c r="C59" s="31"/>
+      <c r="A59" s="40"/>
+      <c r="B59" s="33"/>
+      <c r="C59" s="34"/>
       <c r="D59" s="2" t="s">
         <v>7</v>
       </c>
@@ -5702,9 +6245,9 @@
       </c>
     </row>
     <row r="60" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A60" s="34"/>
-      <c r="B60" s="30"/>
-      <c r="C60" s="25" t="s">
+      <c r="A60" s="40"/>
+      <c r="B60" s="33"/>
+      <c r="C60" s="38" t="s">
         <v>349</v>
       </c>
       <c r="D60" s="2" t="s">
@@ -5727,9 +6270,9 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A61" s="34"/>
-      <c r="B61" s="31"/>
-      <c r="C61" s="26"/>
+      <c r="A61" s="40"/>
+      <c r="B61" s="34"/>
+      <c r="C61" s="39"/>
       <c r="D61" s="2" t="s">
         <v>11</v>
       </c>
@@ -5750,12 +6293,12 @@
       </c>
     </row>
     <row r="62" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A62" s="26"/>
-      <c r="B62" s="27" t="s">
+      <c r="A62" s="39"/>
+      <c r="B62" s="35" t="s">
         <v>355</v>
       </c>
-      <c r="C62" s="37"/>
-      <c r="D62" s="28"/>
+      <c r="C62" s="36"/>
+      <c r="D62" s="37"/>
       <c r="E62" s="9" t="s">
         <v>70</v>
       </c>
@@ -5765,21 +6308,21 @@
       <c r="G62" s="3" t="s">
         <v>419</v>
       </c>
-      <c r="H62" s="39">
+      <c r="H62" s="13">
         <v>8</v>
       </c>
-      <c r="I62" s="40">
+      <c r="I62" s="14">
         <v>11</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A63" s="35" t="s">
+      <c r="A63" s="44" t="s">
         <v>362</v>
       </c>
-      <c r="B63" s="29" t="s">
+      <c r="B63" s="32" t="s">
         <v>348</v>
       </c>
-      <c r="C63" s="29" t="s">
+      <c r="C63" s="32" t="s">
         <v>2</v>
       </c>
       <c r="D63" s="2" t="s">
@@ -5802,9 +6345,9 @@
       </c>
     </row>
     <row r="64" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A64" s="34"/>
-      <c r="B64" s="30"/>
-      <c r="C64" s="30"/>
+      <c r="A64" s="40"/>
+      <c r="B64" s="33"/>
+      <c r="C64" s="33"/>
       <c r="D64" s="2" t="s">
         <v>5</v>
       </c>
@@ -5825,9 +6368,9 @@
       </c>
     </row>
     <row r="65" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A65" s="34"/>
-      <c r="B65" s="30"/>
-      <c r="C65" s="31"/>
+      <c r="A65" s="40"/>
+      <c r="B65" s="33"/>
+      <c r="C65" s="34"/>
       <c r="D65" s="2" t="s">
         <v>7</v>
       </c>
@@ -5848,9 +6391,9 @@
       </c>
     </row>
     <row r="66" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A66" s="34"/>
-      <c r="B66" s="30"/>
-      <c r="C66" s="25" t="s">
+      <c r="A66" s="40"/>
+      <c r="B66" s="33"/>
+      <c r="C66" s="38" t="s">
         <v>349</v>
       </c>
       <c r="D66" s="2" t="s">
@@ -5873,9 +6416,9 @@
       </c>
     </row>
     <row r="67" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A67" s="26"/>
-      <c r="B67" s="31"/>
-      <c r="C67" s="26"/>
+      <c r="A67" s="39"/>
+      <c r="B67" s="34"/>
+      <c r="C67" s="39"/>
       <c r="D67" s="2" t="s">
         <v>11</v>
       </c>
@@ -5896,13 +6439,13 @@
       </c>
     </row>
     <row r="68" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A68" s="25" t="s">
+      <c r="A68" s="38" t="s">
         <v>363</v>
       </c>
-      <c r="B68" s="29" t="s">
+      <c r="B68" s="32" t="s">
         <v>348</v>
       </c>
-      <c r="C68" s="29" t="s">
+      <c r="C68" s="32" t="s">
         <v>2</v>
       </c>
       <c r="D68" s="2" t="s">
@@ -5925,9 +6468,9 @@
       </c>
     </row>
     <row r="69" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A69" s="34"/>
-      <c r="B69" s="30"/>
-      <c r="C69" s="30"/>
+      <c r="A69" s="40"/>
+      <c r="B69" s="33"/>
+      <c r="C69" s="33"/>
       <c r="D69" s="2" t="s">
         <v>5</v>
       </c>
@@ -5948,9 +6491,9 @@
       </c>
     </row>
     <row r="70" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A70" s="34"/>
-      <c r="B70" s="30"/>
-      <c r="C70" s="31"/>
+      <c r="A70" s="40"/>
+      <c r="B70" s="33"/>
+      <c r="C70" s="34"/>
       <c r="D70" s="2" t="s">
         <v>7</v>
       </c>
@@ -5971,9 +6514,9 @@
       </c>
     </row>
     <row r="71" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A71" s="34"/>
-      <c r="B71" s="30"/>
-      <c r="C71" s="25" t="s">
+      <c r="A71" s="40"/>
+      <c r="B71" s="33"/>
+      <c r="C71" s="38" t="s">
         <v>349</v>
       </c>
       <c r="D71" s="2" t="s">
@@ -5996,9 +6539,9 @@
       </c>
     </row>
     <row r="72" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A72" s="26"/>
-      <c r="B72" s="31"/>
-      <c r="C72" s="26"/>
+      <c r="A72" s="39"/>
+      <c r="B72" s="34"/>
+      <c r="C72" s="39"/>
       <c r="D72" s="2" t="s">
         <v>11</v>
       </c>
@@ -6019,13 +6562,13 @@
       </c>
     </row>
     <row r="73" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A73" s="25" t="s">
+      <c r="A73" s="38" t="s">
         <v>364</v>
       </c>
-      <c r="B73" s="29" t="s">
+      <c r="B73" s="32" t="s">
         <v>348</v>
       </c>
-      <c r="C73" s="29" t="s">
+      <c r="C73" s="32" t="s">
         <v>2</v>
       </c>
       <c r="D73" s="2" t="s">
@@ -6048,9 +6591,9 @@
       </c>
     </row>
     <row r="74" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A74" s="34"/>
-      <c r="B74" s="30"/>
-      <c r="C74" s="30"/>
+      <c r="A74" s="40"/>
+      <c r="B74" s="33"/>
+      <c r="C74" s="33"/>
       <c r="D74" s="2" t="s">
         <v>5</v>
       </c>
@@ -6071,9 +6614,9 @@
       </c>
     </row>
     <row r="75" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A75" s="34"/>
-      <c r="B75" s="30"/>
-      <c r="C75" s="31"/>
+      <c r="A75" s="40"/>
+      <c r="B75" s="33"/>
+      <c r="C75" s="34"/>
       <c r="D75" s="2" t="s">
         <v>7</v>
       </c>
@@ -6094,9 +6637,9 @@
       </c>
     </row>
     <row r="76" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A76" s="34"/>
-      <c r="B76" s="30"/>
-      <c r="C76" s="25" t="s">
+      <c r="A76" s="40"/>
+      <c r="B76" s="33"/>
+      <c r="C76" s="38" t="s">
         <v>349</v>
       </c>
       <c r="D76" s="2" t="s">
@@ -6119,9 +6662,9 @@
       </c>
     </row>
     <row r="77" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A77" s="26"/>
-      <c r="B77" s="31"/>
-      <c r="C77" s="26"/>
+      <c r="A77" s="39"/>
+      <c r="B77" s="34"/>
+      <c r="C77" s="39"/>
       <c r="D77" s="2" t="s">
         <v>11</v>
       </c>
@@ -6142,13 +6685,13 @@
       </c>
     </row>
     <row r="78" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A78" s="25" t="s">
+      <c r="A78" s="38" t="s">
         <v>365</v>
       </c>
-      <c r="B78" s="29" t="s">
+      <c r="B78" s="32" t="s">
         <v>348</v>
       </c>
-      <c r="C78" s="29" t="s">
+      <c r="C78" s="32" t="s">
         <v>2</v>
       </c>
       <c r="D78" s="2" t="s">
@@ -6171,9 +6714,9 @@
       </c>
     </row>
     <row r="79" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A79" s="34"/>
-      <c r="B79" s="30"/>
-      <c r="C79" s="30"/>
+      <c r="A79" s="40"/>
+      <c r="B79" s="33"/>
+      <c r="C79" s="33"/>
       <c r="D79" s="2" t="s">
         <v>5</v>
       </c>
@@ -6194,9 +6737,9 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A80" s="34"/>
-      <c r="B80" s="30"/>
-      <c r="C80" s="31"/>
+      <c r="A80" s="40"/>
+      <c r="B80" s="33"/>
+      <c r="C80" s="34"/>
       <c r="D80" s="2" t="s">
         <v>7</v>
       </c>
@@ -6217,9 +6760,9 @@
       </c>
     </row>
     <row r="81" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A81" s="34"/>
-      <c r="B81" s="30"/>
-      <c r="C81" s="25" t="s">
+      <c r="A81" s="40"/>
+      <c r="B81" s="33"/>
+      <c r="C81" s="38" t="s">
         <v>349</v>
       </c>
       <c r="D81" s="2" t="s">
@@ -6242,9 +6785,9 @@
       </c>
     </row>
     <row r="82" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A82" s="26"/>
-      <c r="B82" s="31"/>
-      <c r="C82" s="26"/>
+      <c r="A82" s="39"/>
+      <c r="B82" s="34"/>
+      <c r="C82" s="39"/>
       <c r="D82" s="2" t="s">
         <v>11</v>
       </c>
@@ -6265,13 +6808,13 @@
       </c>
     </row>
     <row r="83" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A83" s="25" t="s">
+      <c r="A83" s="38" t="s">
         <v>366</v>
       </c>
-      <c r="B83" s="29" t="s">
+      <c r="B83" s="32" t="s">
         <v>348</v>
       </c>
-      <c r="C83" s="29" t="s">
+      <c r="C83" s="32" t="s">
         <v>2</v>
       </c>
       <c r="D83" s="2" t="s">
@@ -6294,9 +6837,9 @@
       </c>
     </row>
     <row r="84" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A84" s="34"/>
-      <c r="B84" s="30"/>
-      <c r="C84" s="30"/>
+      <c r="A84" s="40"/>
+      <c r="B84" s="33"/>
+      <c r="C84" s="33"/>
       <c r="D84" s="2" t="s">
         <v>5</v>
       </c>
@@ -6317,9 +6860,9 @@
       </c>
     </row>
     <row r="85" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A85" s="34"/>
-      <c r="B85" s="30"/>
-      <c r="C85" s="31"/>
+      <c r="A85" s="40"/>
+      <c r="B85" s="33"/>
+      <c r="C85" s="34"/>
       <c r="D85" s="2" t="s">
         <v>7</v>
       </c>
@@ -6340,9 +6883,9 @@
       </c>
     </row>
     <row r="86" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A86" s="34"/>
-      <c r="B86" s="30"/>
-      <c r="C86" s="25" t="s">
+      <c r="A86" s="40"/>
+      <c r="B86" s="33"/>
+      <c r="C86" s="38" t="s">
         <v>349</v>
       </c>
       <c r="D86" s="2" t="s">
@@ -6365,9 +6908,9 @@
       </c>
     </row>
     <row r="87" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A87" s="34"/>
-      <c r="B87" s="31"/>
-      <c r="C87" s="26"/>
+      <c r="A87" s="40"/>
+      <c r="B87" s="34"/>
+      <c r="C87" s="39"/>
       <c r="D87" s="2" t="s">
         <v>11</v>
       </c>
@@ -6388,11 +6931,11 @@
       </c>
     </row>
     <row r="88" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A88" s="26"/>
-      <c r="B88" s="27" t="s">
+      <c r="A88" s="39"/>
+      <c r="B88" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="C88" s="28"/>
+      <c r="C88" s="37"/>
       <c r="D88" s="2"/>
       <c r="E88" s="9" t="s">
         <v>382</v>
@@ -6403,21 +6946,21 @@
       <c r="G88" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="H88" s="39">
+      <c r="H88" s="13">
         <v>8</v>
       </c>
-      <c r="I88" s="40">
+      <c r="I88" s="14">
         <v>11</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A89" s="35" t="s">
+      <c r="A89" s="44" t="s">
         <v>367</v>
       </c>
-      <c r="B89" s="29" t="s">
+      <c r="B89" s="32" t="s">
         <v>348</v>
       </c>
-      <c r="C89" s="29" t="s">
+      <c r="C89" s="32" t="s">
         <v>2</v>
       </c>
       <c r="D89" s="2" t="s">
@@ -6440,9 +6983,9 @@
       </c>
     </row>
     <row r="90" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A90" s="34"/>
-      <c r="B90" s="30"/>
-      <c r="C90" s="30"/>
+      <c r="A90" s="40"/>
+      <c r="B90" s="33"/>
+      <c r="C90" s="33"/>
       <c r="D90" s="2" t="s">
         <v>5</v>
       </c>
@@ -6463,9 +7006,9 @@
       </c>
     </row>
     <row r="91" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A91" s="34"/>
-      <c r="B91" s="30"/>
-      <c r="C91" s="31"/>
+      <c r="A91" s="40"/>
+      <c r="B91" s="33"/>
+      <c r="C91" s="34"/>
       <c r="D91" s="2" t="s">
         <v>7</v>
       </c>
@@ -6486,9 +7029,9 @@
       </c>
     </row>
     <row r="92" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A92" s="34"/>
-      <c r="B92" s="30"/>
-      <c r="C92" s="25" t="s">
+      <c r="A92" s="40"/>
+      <c r="B92" s="33"/>
+      <c r="C92" s="38" t="s">
         <v>349</v>
       </c>
       <c r="D92" s="2" t="s">
@@ -6511,9 +7054,9 @@
       </c>
     </row>
     <row r="93" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A93" s="34"/>
-      <c r="B93" s="31"/>
-      <c r="C93" s="26"/>
+      <c r="A93" s="40"/>
+      <c r="B93" s="34"/>
+      <c r="C93" s="39"/>
       <c r="D93" s="2" t="s">
         <v>11</v>
       </c>
@@ -6534,11 +7077,11 @@
       </c>
     </row>
     <row r="94" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A94" s="26"/>
-      <c r="B94" s="27" t="s">
+      <c r="A94" s="39"/>
+      <c r="B94" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="C94" s="28"/>
+      <c r="C94" s="37"/>
       <c r="D94" s="2"/>
       <c r="E94" s="9" t="s">
         <v>388</v>
@@ -6549,21 +7092,21 @@
       <c r="G94" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="H94" s="39">
+      <c r="H94" s="13">
         <v>8</v>
       </c>
-      <c r="I94" s="40">
+      <c r="I94" s="14">
         <v>11</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A95" s="25" t="s">
+      <c r="A95" s="38" t="s">
         <v>368</v>
       </c>
-      <c r="B95" s="29" t="s">
+      <c r="B95" s="32" t="s">
         <v>348</v>
       </c>
-      <c r="C95" s="29" t="s">
+      <c r="C95" s="32" t="s">
         <v>2</v>
       </c>
       <c r="D95" s="2" t="s">
@@ -6586,9 +7129,9 @@
       </c>
     </row>
     <row r="96" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A96" s="34"/>
-      <c r="B96" s="30"/>
-      <c r="C96" s="30"/>
+      <c r="A96" s="40"/>
+      <c r="B96" s="33"/>
+      <c r="C96" s="33"/>
       <c r="D96" s="2" t="s">
         <v>5</v>
       </c>
@@ -6609,9 +7152,9 @@
       </c>
     </row>
     <row r="97" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A97" s="34"/>
-      <c r="B97" s="30"/>
-      <c r="C97" s="31"/>
+      <c r="A97" s="40"/>
+      <c r="B97" s="33"/>
+      <c r="C97" s="34"/>
       <c r="D97" s="2" t="s">
         <v>7</v>
       </c>
@@ -6632,9 +7175,9 @@
       </c>
     </row>
     <row r="98" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A98" s="34"/>
-      <c r="B98" s="30"/>
-      <c r="C98" s="25" t="s">
+      <c r="A98" s="40"/>
+      <c r="B98" s="33"/>
+      <c r="C98" s="38" t="s">
         <v>349</v>
       </c>
       <c r="D98" s="2" t="s">
@@ -6657,9 +7200,9 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A99" s="34"/>
-      <c r="B99" s="31"/>
-      <c r="C99" s="26"/>
+      <c r="A99" s="40"/>
+      <c r="B99" s="34"/>
+      <c r="C99" s="39"/>
       <c r="D99" s="2" t="s">
         <v>11</v>
       </c>
@@ -6680,11 +7223,11 @@
       </c>
     </row>
     <row r="100" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A100" s="26"/>
-      <c r="B100" s="27" t="s">
+      <c r="A100" s="39"/>
+      <c r="B100" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="C100" s="28"/>
+      <c r="C100" s="37"/>
       <c r="D100" s="2"/>
       <c r="E100" s="9" t="s">
         <v>394</v>
@@ -6695,21 +7238,21 @@
       <c r="G100" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="H100" s="39">
+      <c r="H100" s="13">
         <v>8</v>
       </c>
-      <c r="I100" s="40">
+      <c r="I100" s="14">
         <v>11</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A101" s="25" t="s">
+      <c r="A101" s="38" t="s">
         <v>369</v>
       </c>
-      <c r="B101" s="29" t="s">
+      <c r="B101" s="32" t="s">
         <v>348</v>
       </c>
-      <c r="C101" s="29" t="s">
+      <c r="C101" s="32" t="s">
         <v>2</v>
       </c>
       <c r="D101" s="2" t="s">
@@ -6732,9 +7275,9 @@
       </c>
     </row>
     <row r="102" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A102" s="34"/>
-      <c r="B102" s="30"/>
-      <c r="C102" s="30"/>
+      <c r="A102" s="40"/>
+      <c r="B102" s="33"/>
+      <c r="C102" s="33"/>
       <c r="D102" s="2" t="s">
         <v>5</v>
       </c>
@@ -6755,9 +7298,9 @@
       </c>
     </row>
     <row r="103" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A103" s="34"/>
-      <c r="B103" s="30"/>
-      <c r="C103" s="31"/>
+      <c r="A103" s="40"/>
+      <c r="B103" s="33"/>
+      <c r="C103" s="34"/>
       <c r="D103" s="2" t="s">
         <v>7</v>
       </c>
@@ -6778,9 +7321,9 @@
       </c>
     </row>
     <row r="104" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A104" s="34"/>
-      <c r="B104" s="30"/>
-      <c r="C104" s="25" t="s">
+      <c r="A104" s="40"/>
+      <c r="B104" s="33"/>
+      <c r="C104" s="38" t="s">
         <v>349</v>
       </c>
       <c r="D104" s="2" t="s">
@@ -6803,9 +7346,9 @@
       </c>
     </row>
     <row r="105" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A105" s="34"/>
-      <c r="B105" s="31"/>
-      <c r="C105" s="26"/>
+      <c r="A105" s="40"/>
+      <c r="B105" s="34"/>
+      <c r="C105" s="39"/>
       <c r="D105" s="2" t="s">
         <v>11</v>
       </c>
@@ -6826,11 +7369,11 @@
       </c>
     </row>
     <row r="106" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A106" s="26"/>
-      <c r="B106" s="27" t="s">
+      <c r="A106" s="39"/>
+      <c r="B106" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="C106" s="28"/>
+      <c r="C106" s="37"/>
       <c r="D106" s="2"/>
       <c r="E106" s="9" t="s">
         <v>400</v>
@@ -6841,21 +7384,21 @@
       <c r="G106" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="H106" s="39">
+      <c r="H106" s="13">
         <v>8</v>
       </c>
-      <c r="I106" s="40">
+      <c r="I106" s="14">
         <v>11</v>
       </c>
     </row>
     <row r="107" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A107" s="25" t="s">
+      <c r="A107" s="38" t="s">
         <v>370</v>
       </c>
-      <c r="B107" s="29" t="s">
+      <c r="B107" s="32" t="s">
         <v>348</v>
       </c>
-      <c r="C107" s="29" t="s">
+      <c r="C107" s="32" t="s">
         <v>2</v>
       </c>
       <c r="D107" s="2" t="s">
@@ -6878,9 +7421,9 @@
       </c>
     </row>
     <row r="108" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A108" s="34"/>
-      <c r="B108" s="30"/>
-      <c r="C108" s="30"/>
+      <c r="A108" s="40"/>
+      <c r="B108" s="33"/>
+      <c r="C108" s="33"/>
       <c r="D108" s="2" t="s">
         <v>5</v>
       </c>
@@ -6901,9 +7444,9 @@
       </c>
     </row>
     <row r="109" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A109" s="34"/>
-      <c r="B109" s="30"/>
-      <c r="C109" s="31"/>
+      <c r="A109" s="40"/>
+      <c r="B109" s="33"/>
+      <c r="C109" s="34"/>
       <c r="D109" s="2" t="s">
         <v>7</v>
       </c>
@@ -6924,9 +7467,9 @@
       </c>
     </row>
     <row r="110" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A110" s="34"/>
-      <c r="B110" s="30"/>
-      <c r="C110" s="25" t="s">
+      <c r="A110" s="40"/>
+      <c r="B110" s="33"/>
+      <c r="C110" s="38" t="s">
         <v>349</v>
       </c>
       <c r="D110" s="2" t="s">
@@ -6949,9 +7492,9 @@
       </c>
     </row>
     <row r="111" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A111" s="34"/>
-      <c r="B111" s="31"/>
-      <c r="C111" s="26"/>
+      <c r="A111" s="40"/>
+      <c r="B111" s="34"/>
+      <c r="C111" s="39"/>
       <c r="D111" s="2" t="s">
         <v>11</v>
       </c>
@@ -6972,11 +7515,11 @@
       </c>
     </row>
     <row r="112" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A112" s="26"/>
-      <c r="B112" s="32" t="s">
+      <c r="A112" s="39"/>
+      <c r="B112" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="C112" s="33"/>
+      <c r="C112" s="43"/>
       <c r="D112" s="2"/>
       <c r="E112" s="9" t="s">
         <v>406</v>
@@ -6987,21 +7530,21 @@
       <c r="G112" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="H112" s="39">
+      <c r="H112" s="13">
         <v>8</v>
       </c>
-      <c r="I112" s="40">
+      <c r="I112" s="14">
         <v>11</v>
       </c>
     </row>
     <row r="113" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A113" s="25" t="s">
+      <c r="A113" s="38" t="s">
         <v>371</v>
       </c>
-      <c r="B113" s="29" t="s">
+      <c r="B113" s="32" t="s">
         <v>348</v>
       </c>
-      <c r="C113" s="29" t="s">
+      <c r="C113" s="32" t="s">
         <v>2</v>
       </c>
       <c r="D113" s="2" t="s">
@@ -7024,9 +7567,9 @@
       </c>
     </row>
     <row r="114" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A114" s="34"/>
-      <c r="B114" s="30"/>
-      <c r="C114" s="30"/>
+      <c r="A114" s="40"/>
+      <c r="B114" s="33"/>
+      <c r="C114" s="33"/>
       <c r="D114" s="2" t="s">
         <v>5</v>
       </c>
@@ -7047,9 +7590,9 @@
       </c>
     </row>
     <row r="115" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A115" s="34"/>
-      <c r="B115" s="30"/>
-      <c r="C115" s="31"/>
+      <c r="A115" s="40"/>
+      <c r="B115" s="33"/>
+      <c r="C115" s="34"/>
       <c r="D115" s="2" t="s">
         <v>7</v>
       </c>
@@ -7070,9 +7613,9 @@
       </c>
     </row>
     <row r="116" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A116" s="34"/>
-      <c r="B116" s="30"/>
-      <c r="C116" s="25" t="s">
+      <c r="A116" s="40"/>
+      <c r="B116" s="33"/>
+      <c r="C116" s="38" t="s">
         <v>349</v>
       </c>
       <c r="D116" s="2" t="s">
@@ -7095,9 +7638,9 @@
       </c>
     </row>
     <row r="117" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A117" s="34"/>
-      <c r="B117" s="31"/>
-      <c r="C117" s="26"/>
+      <c r="A117" s="40"/>
+      <c r="B117" s="34"/>
+      <c r="C117" s="39"/>
       <c r="D117" s="2" t="s">
         <v>11</v>
       </c>
@@ -7118,11 +7661,11 @@
       </c>
     </row>
     <row r="118" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A118" s="26"/>
-      <c r="B118" s="27" t="s">
+      <c r="A118" s="39"/>
+      <c r="B118" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="C118" s="28"/>
+      <c r="C118" s="37"/>
       <c r="D118" s="2"/>
       <c r="E118" s="9" t="s">
         <v>412</v>
@@ -7133,21 +7676,21 @@
       <c r="G118" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="H118" s="39">
+      <c r="H118" s="13">
         <v>8</v>
       </c>
-      <c r="I118" s="40">
+      <c r="I118" s="14">
         <v>11</v>
       </c>
     </row>
     <row r="119" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A119" s="35" t="s">
+      <c r="A119" s="44" t="s">
         <v>372</v>
       </c>
-      <c r="B119" s="29" t="s">
+      <c r="B119" s="32" t="s">
         <v>348</v>
       </c>
-      <c r="C119" s="29" t="s">
+      <c r="C119" s="32" t="s">
         <v>2</v>
       </c>
       <c r="D119" s="2" t="s">
@@ -7170,9 +7713,9 @@
       </c>
     </row>
     <row r="120" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A120" s="34"/>
-      <c r="B120" s="30"/>
-      <c r="C120" s="30"/>
+      <c r="A120" s="40"/>
+      <c r="B120" s="33"/>
+      <c r="C120" s="33"/>
       <c r="D120" s="2" t="s">
         <v>5</v>
       </c>
@@ -7193,9 +7736,9 @@
       </c>
     </row>
     <row r="121" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A121" s="34"/>
-      <c r="B121" s="30"/>
-      <c r="C121" s="31"/>
+      <c r="A121" s="40"/>
+      <c r="B121" s="33"/>
+      <c r="C121" s="34"/>
       <c r="D121" s="2" t="s">
         <v>7</v>
       </c>
@@ -7216,9 +7759,9 @@
       </c>
     </row>
     <row r="122" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A122" s="34"/>
-      <c r="B122" s="30"/>
-      <c r="C122" s="25" t="s">
+      <c r="A122" s="40"/>
+      <c r="B122" s="33"/>
+      <c r="C122" s="38" t="s">
         <v>349</v>
       </c>
       <c r="D122" s="2" t="s">
@@ -7241,9 +7784,9 @@
       </c>
     </row>
     <row r="123" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A123" s="34"/>
-      <c r="B123" s="31"/>
-      <c r="C123" s="26"/>
+      <c r="A123" s="40"/>
+      <c r="B123" s="34"/>
+      <c r="C123" s="39"/>
       <c r="D123" s="2" t="s">
         <v>11</v>
       </c>
@@ -7264,11 +7807,11 @@
       </c>
     </row>
     <row r="124" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A124" s="26"/>
-      <c r="B124" s="32" t="s">
+      <c r="A124" s="39"/>
+      <c r="B124" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="C124" s="33"/>
+      <c r="C124" s="43"/>
       <c r="D124" s="2"/>
       <c r="E124" s="9" t="s">
         <v>418</v>
@@ -7279,75 +7822,34 @@
       <c r="G124" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="H124" s="39">
+      <c r="H124" s="13">
         <v>8</v>
       </c>
-      <c r="I124" s="40">
+      <c r="I124" s="14">
         <v>11</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="103">
-    <mergeCell ref="A7:A12"/>
-    <mergeCell ref="B7:B11"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="A1:A6"/>
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B1:B5"/>
-    <mergeCell ref="A20:A26"/>
-    <mergeCell ref="B20:B24"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="A13:A19"/>
-    <mergeCell ref="B13:B17"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B33:B37"/>
-    <mergeCell ref="A39:A44"/>
-    <mergeCell ref="B39:B43"/>
-    <mergeCell ref="C39:C41"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="A27:A32"/>
-    <mergeCell ref="C27:C29"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B27:B31"/>
-    <mergeCell ref="A33:A38"/>
-    <mergeCell ref="C33:C35"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="A45:A50"/>
-    <mergeCell ref="B45:B49"/>
-    <mergeCell ref="C45:C47"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="A51:A56"/>
-    <mergeCell ref="B51:B55"/>
-    <mergeCell ref="C51:C53"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="A63:A67"/>
-    <mergeCell ref="C63:C65"/>
-    <mergeCell ref="B63:B67"/>
-    <mergeCell ref="C66:C67"/>
-    <mergeCell ref="A68:A72"/>
-    <mergeCell ref="C68:C70"/>
-    <mergeCell ref="B68:B72"/>
-    <mergeCell ref="C71:C72"/>
-    <mergeCell ref="A57:A62"/>
-    <mergeCell ref="C57:C59"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="B57:B61"/>
-    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="C86:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B89:B93"/>
+    <mergeCell ref="C89:C91"/>
+    <mergeCell ref="C92:C93"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="C119:C121"/>
+    <mergeCell ref="C122:C123"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B113:B117"/>
+    <mergeCell ref="C113:C115"/>
+    <mergeCell ref="C116:C117"/>
+    <mergeCell ref="B119:B123"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B107:B111"/>
+    <mergeCell ref="C107:C109"/>
+    <mergeCell ref="C110:C111"/>
+    <mergeCell ref="B112:C112"/>
     <mergeCell ref="A101:A106"/>
     <mergeCell ref="A107:A112"/>
     <mergeCell ref="A113:A118"/>
@@ -7372,28 +7874,1603 @@
     <mergeCell ref="C104:C105"/>
     <mergeCell ref="B83:B87"/>
     <mergeCell ref="C83:C85"/>
-    <mergeCell ref="C86:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B89:B93"/>
-    <mergeCell ref="C89:C91"/>
-    <mergeCell ref="C92:C93"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="C119:C121"/>
-    <mergeCell ref="C122:C123"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B113:B117"/>
-    <mergeCell ref="C113:C115"/>
-    <mergeCell ref="C116:C117"/>
-    <mergeCell ref="B119:B123"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B107:B111"/>
-    <mergeCell ref="C107:C109"/>
-    <mergeCell ref="C110:C111"/>
-    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="A63:A67"/>
+    <mergeCell ref="C63:C65"/>
+    <mergeCell ref="B63:B67"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="A68:A72"/>
+    <mergeCell ref="C68:C70"/>
+    <mergeCell ref="B68:B72"/>
+    <mergeCell ref="C71:C72"/>
+    <mergeCell ref="A57:A62"/>
+    <mergeCell ref="C57:C59"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="B57:B61"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="A45:A50"/>
+    <mergeCell ref="B45:B49"/>
+    <mergeCell ref="C45:C47"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="A51:A56"/>
+    <mergeCell ref="B51:B55"/>
+    <mergeCell ref="C51:C53"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="B33:B37"/>
+    <mergeCell ref="A39:A44"/>
+    <mergeCell ref="B39:B43"/>
+    <mergeCell ref="C39:C41"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="A27:A32"/>
+    <mergeCell ref="C27:C29"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B27:B31"/>
+    <mergeCell ref="A33:A38"/>
+    <mergeCell ref="C33:C35"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="A20:A26"/>
+    <mergeCell ref="B20:B24"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="A13:A19"/>
+    <mergeCell ref="B13:B17"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A7:A12"/>
+    <mergeCell ref="B7:B11"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="A1:A6"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B1:B5"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE06F252-EF64-45F6-9EF1-8A2C189CFD60}">
+  <dimension ref="A1:G72"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="37" customWidth="1"/>
+    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="42.140625" customWidth="1"/>
+    <col min="5" max="5" width="27.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="47" t="s">
+        <v>421</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>423</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="50">
+        <v>110</v>
+      </c>
+      <c r="G1" s="50">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="48"/>
+      <c r="B2" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>425</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" s="50">
+        <v>110</v>
+      </c>
+      <c r="G2" s="50">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="48"/>
+      <c r="B3" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>427</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="50">
+        <v>110</v>
+      </c>
+      <c r="G3" s="50">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="48"/>
+      <c r="B4" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>429</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="50">
+        <v>75</v>
+      </c>
+      <c r="G4" s="50">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="48"/>
+      <c r="B5" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>431</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="50">
+        <v>75</v>
+      </c>
+      <c r="G5" s="50">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="49"/>
+      <c r="B6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>432</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="F6" s="51">
+        <v>365</v>
+      </c>
+      <c r="G6" s="51">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A7" s="47" t="s">
+        <v>433</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>434</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="50">
+        <v>110</v>
+      </c>
+      <c r="G7" s="50">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="48"/>
+      <c r="B8" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>435</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="50">
+        <v>110</v>
+      </c>
+      <c r="G8" s="50">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="48"/>
+      <c r="B9" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>436</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" s="50">
+        <v>110</v>
+      </c>
+      <c r="G9" s="50">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="48"/>
+      <c r="B10" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>438</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="50">
+        <v>75</v>
+      </c>
+      <c r="G10" s="50">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="48"/>
+      <c r="B11" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>440</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="52">
+        <v>75</v>
+      </c>
+      <c r="G11" s="52">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="48"/>
+      <c r="B12" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>442</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="53">
+        <v>90</v>
+      </c>
+      <c r="G12" s="53">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="48"/>
+      <c r="B13" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>444</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="53">
+        <v>90</v>
+      </c>
+      <c r="G13" s="53">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+      <c r="A14" s="49"/>
+      <c r="B14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>445</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+    </row>
+    <row r="15" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="47" t="s">
+        <v>446</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>447</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" s="53">
+        <v>110</v>
+      </c>
+      <c r="G15" s="53">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A16" s="48"/>
+      <c r="B16" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>448</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F16" s="53">
+        <v>110</v>
+      </c>
+      <c r="G16" s="53">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A17" s="48"/>
+      <c r="B17" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>449</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F17" s="53">
+        <v>110</v>
+      </c>
+      <c r="G17" s="53">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+      <c r="A18" s="48"/>
+      <c r="B18" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>450</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F18" s="53">
+        <v>80</v>
+      </c>
+      <c r="G18" s="53">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+      <c r="A19" s="48"/>
+      <c r="B19" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>451</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F19" s="53">
+        <v>80</v>
+      </c>
+      <c r="G19" s="53">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A20" s="48"/>
+      <c r="B20" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>453</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" s="53">
+        <v>80</v>
+      </c>
+      <c r="G20" s="53">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+      <c r="A21" s="48"/>
+      <c r="B21" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>455</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F21" s="53">
+        <v>80</v>
+      </c>
+      <c r="G21" s="53">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+      <c r="A22" s="48"/>
+      <c r="B22" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>457</v>
+      </c>
+      <c r="E22" s="19" t="s">
+        <v>458</v>
+      </c>
+      <c r="F22" s="19">
+        <v>9</v>
+      </c>
+      <c r="G22" s="19">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+      <c r="A23" s="48"/>
+      <c r="B23" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>460</v>
+      </c>
+      <c r="E23" s="19" t="s">
+        <v>458</v>
+      </c>
+      <c r="F23" s="19">
+        <v>9</v>
+      </c>
+      <c r="G23" s="19">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+      <c r="A24" s="48"/>
+      <c r="B24" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>462</v>
+      </c>
+      <c r="E24" s="19" t="s">
+        <v>458</v>
+      </c>
+      <c r="F24" s="19">
+        <v>9</v>
+      </c>
+      <c r="G24" s="19">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+      <c r="A25" s="48"/>
+      <c r="B25" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>464</v>
+      </c>
+      <c r="E25" s="19" t="s">
+        <v>458</v>
+      </c>
+      <c r="F25" s="19">
+        <v>9</v>
+      </c>
+      <c r="G25" s="19">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+      <c r="A26" s="49"/>
+      <c r="B26" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>465</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="F26" s="54">
+        <v>120</v>
+      </c>
+      <c r="G26" s="54">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>468</v>
+      </c>
+      <c r="E27" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="F27" s="19">
+        <v>10</v>
+      </c>
+      <c r="G27" s="19">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A28" s="18" t="s">
+        <v>469</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>471</v>
+      </c>
+      <c r="E28" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="F28" s="19">
+        <v>5</v>
+      </c>
+      <c r="G28" s="19">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A29" s="18" t="s">
+        <v>472</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="D29" s="16" t="s">
+        <v>474</v>
+      </c>
+      <c r="E29" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="F29" s="19">
+        <v>5</v>
+      </c>
+      <c r="G29" s="1"/>
+    </row>
+    <row r="30" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A30" s="46" t="s">
+        <v>475</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>477</v>
+      </c>
+      <c r="E30" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="F30" s="53">
+        <v>90</v>
+      </c>
+      <c r="G30" s="1"/>
+    </row>
+    <row r="31" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A31" s="46"/>
+      <c r="B31" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D31" s="16" t="s">
+        <v>479</v>
+      </c>
+      <c r="E31" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="F31" s="53">
+        <v>90</v>
+      </c>
+      <c r="G31" s="1"/>
+    </row>
+    <row r="32" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A32" s="46"/>
+      <c r="B32" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>480</v>
+      </c>
+      <c r="E32" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="F32" s="55">
+        <v>35</v>
+      </c>
+      <c r="G32" s="54">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+      <c r="A33" s="46" t="s">
+        <v>481</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="D33" s="16" t="s">
+        <v>482</v>
+      </c>
+      <c r="E33" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="F33" s="54">
+        <v>90</v>
+      </c>
+      <c r="G33" s="1"/>
+    </row>
+    <row r="34" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A34" s="46"/>
+      <c r="B34" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="D34" s="16" t="s">
+        <v>483</v>
+      </c>
+      <c r="E34" s="19" t="s">
+        <v>419</v>
+      </c>
+      <c r="F34" s="54">
+        <v>150</v>
+      </c>
+      <c r="G34" s="1"/>
+    </row>
+    <row r="35" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A35" s="46" t="s">
+        <v>484</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D35" s="16" t="s">
+        <v>486</v>
+      </c>
+      <c r="E35" s="19" t="s">
+        <v>487</v>
+      </c>
+      <c r="F35" s="55">
+        <v>350</v>
+      </c>
+      <c r="G35" s="1"/>
+    </row>
+    <row r="36" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A36" s="46"/>
+      <c r="B36" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="D36" s="16" t="s">
+        <v>489</v>
+      </c>
+      <c r="E36" s="19" t="s">
+        <v>487</v>
+      </c>
+      <c r="F36" s="55">
+        <v>350</v>
+      </c>
+      <c r="G36" s="1"/>
+    </row>
+    <row r="37" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A37" s="46"/>
+      <c r="B37" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="D37" s="16" t="s">
+        <v>491</v>
+      </c>
+      <c r="E37" s="19" t="s">
+        <v>487</v>
+      </c>
+      <c r="F37" s="55">
+        <v>350</v>
+      </c>
+      <c r="G37" s="1"/>
+    </row>
+    <row r="38" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A38" s="46"/>
+      <c r="B38" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="D38" s="16" t="s">
+        <v>493</v>
+      </c>
+      <c r="E38" s="19" t="s">
+        <v>494</v>
+      </c>
+      <c r="F38" s="53">
+        <v>80</v>
+      </c>
+      <c r="G38" s="1"/>
+    </row>
+    <row r="39" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A39" s="46"/>
+      <c r="B39" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="D39" s="16" t="s">
+        <v>496</v>
+      </c>
+      <c r="E39" s="19" t="s">
+        <v>494</v>
+      </c>
+      <c r="F39" s="53">
+        <v>80</v>
+      </c>
+      <c r="G39" s="1"/>
+    </row>
+    <row r="40" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A40" s="46"/>
+      <c r="B40" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="C40" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="D40" s="16" t="s">
+        <v>498</v>
+      </c>
+      <c r="E40" s="19" t="s">
+        <v>494</v>
+      </c>
+      <c r="F40" s="53">
+        <v>80</v>
+      </c>
+      <c r="G40" s="1"/>
+    </row>
+    <row r="41" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A41" s="46" t="s">
+        <v>499</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="C41" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="D41" s="16" t="s">
+        <v>501</v>
+      </c>
+      <c r="E41" s="19" t="s">
+        <v>502</v>
+      </c>
+      <c r="F41" s="53">
+        <v>13</v>
+      </c>
+      <c r="G41" s="56">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A42" s="46"/>
+      <c r="B42" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C42" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="D42" s="16" t="s">
+        <v>504</v>
+      </c>
+      <c r="E42" s="19" t="s">
+        <v>502</v>
+      </c>
+      <c r="F42" s="53">
+        <v>13</v>
+      </c>
+      <c r="G42" s="56">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A43" s="46"/>
+      <c r="B43" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="C43" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="D43" s="16" t="s">
+        <v>506</v>
+      </c>
+      <c r="E43" s="19" t="s">
+        <v>502</v>
+      </c>
+      <c r="F43" s="53">
+        <v>13</v>
+      </c>
+      <c r="G43" s="56">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A44" s="46"/>
+      <c r="B44" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="C44" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D44" s="16" t="s">
+        <v>508</v>
+      </c>
+      <c r="E44" s="19" t="s">
+        <v>502</v>
+      </c>
+      <c r="F44" s="53">
+        <v>13</v>
+      </c>
+      <c r="G44" s="56">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A45" s="46"/>
+      <c r="B45" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="C45" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="D45" s="16" t="s">
+        <v>510</v>
+      </c>
+      <c r="E45" s="19" t="s">
+        <v>502</v>
+      </c>
+      <c r="F45" s="53">
+        <v>13</v>
+      </c>
+      <c r="G45" s="56">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A46" s="46"/>
+      <c r="B46" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="C46" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="D46" s="16" t="s">
+        <v>512</v>
+      </c>
+      <c r="E46" s="19" t="s">
+        <v>502</v>
+      </c>
+      <c r="F46" s="53">
+        <v>13</v>
+      </c>
+      <c r="G46" s="56">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A47" s="46"/>
+      <c r="B47" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="C47" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="D47" s="16" t="s">
+        <v>514</v>
+      </c>
+      <c r="E47" s="19" t="s">
+        <v>502</v>
+      </c>
+      <c r="F47" s="53">
+        <v>13</v>
+      </c>
+      <c r="G47" s="56">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A48" s="46"/>
+      <c r="B48" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="C48" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="D48" s="16" t="s">
+        <v>516</v>
+      </c>
+      <c r="E48" s="19" t="s">
+        <v>502</v>
+      </c>
+      <c r="F48" s="53">
+        <v>13</v>
+      </c>
+      <c r="G48" s="56">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A49" s="46"/>
+      <c r="B49" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="C49" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="D49" s="16" t="s">
+        <v>518</v>
+      </c>
+      <c r="E49" s="19" t="s">
+        <v>502</v>
+      </c>
+      <c r="F49" s="53">
+        <v>13</v>
+      </c>
+      <c r="G49" s="56">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A50" s="46"/>
+      <c r="B50" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="C50" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="D50" s="16" t="s">
+        <v>520</v>
+      </c>
+      <c r="E50" s="19" t="s">
+        <v>502</v>
+      </c>
+      <c r="F50" s="53">
+        <v>13</v>
+      </c>
+      <c r="G50" s="56">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A51" s="46"/>
+      <c r="B51" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="C51" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="D51" s="16" t="s">
+        <v>522</v>
+      </c>
+      <c r="E51" s="19" t="s">
+        <v>502</v>
+      </c>
+      <c r="F51" s="53">
+        <v>13</v>
+      </c>
+      <c r="G51" s="56">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A52" s="46"/>
+      <c r="B52" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="C52" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="D52" s="16" t="s">
+        <v>524</v>
+      </c>
+      <c r="E52" s="19" t="s">
+        <v>502</v>
+      </c>
+      <c r="F52" s="53">
+        <v>13</v>
+      </c>
+      <c r="G52" s="56">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A53" s="46"/>
+      <c r="B53" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="C53" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="D53" s="16" t="s">
+        <v>526</v>
+      </c>
+      <c r="E53" s="19" t="s">
+        <v>502</v>
+      </c>
+      <c r="F53" s="53">
+        <v>13</v>
+      </c>
+      <c r="G53" s="56">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A54" s="46"/>
+      <c r="B54" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="C54" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="D54" s="16" t="s">
+        <v>528</v>
+      </c>
+      <c r="E54" s="19" t="s">
+        <v>502</v>
+      </c>
+      <c r="F54" s="53">
+        <v>13</v>
+      </c>
+      <c r="G54" s="56">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A55" s="46"/>
+      <c r="B55" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="C55" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="D55" s="16" t="s">
+        <v>530</v>
+      </c>
+      <c r="E55" s="19" t="s">
+        <v>502</v>
+      </c>
+      <c r="F55" s="53">
+        <v>13</v>
+      </c>
+      <c r="G55" s="56">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A56" s="46"/>
+      <c r="B56" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="C56" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="D56" s="16" t="s">
+        <v>532</v>
+      </c>
+      <c r="E56" s="19" t="s">
+        <v>502</v>
+      </c>
+      <c r="F56" s="53">
+        <v>13</v>
+      </c>
+      <c r="G56" s="56">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A57" s="46"/>
+      <c r="B57" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="C57" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="D57" s="16" t="s">
+        <v>534</v>
+      </c>
+      <c r="E57" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="F57" s="19">
+        <v>75</v>
+      </c>
+      <c r="G57" s="19">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A58" s="46"/>
+      <c r="B58" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="C58" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="D58" s="16" t="s">
+        <v>536</v>
+      </c>
+      <c r="E58" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="F58" s="19">
+        <v>75</v>
+      </c>
+      <c r="G58" s="19">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A59" s="46"/>
+      <c r="B59" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="C59" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="D59" s="16" t="s">
+        <v>538</v>
+      </c>
+      <c r="E59" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="F59" s="19">
+        <v>75</v>
+      </c>
+      <c r="G59" s="19">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A60" s="46"/>
+      <c r="B60" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="C60" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="D60" s="16" t="s">
+        <v>540</v>
+      </c>
+      <c r="E60" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="F60" s="19">
+        <v>75</v>
+      </c>
+      <c r="G60" s="19">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A61" s="46"/>
+      <c r="B61" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="C61" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="D61" s="16" t="s">
+        <v>542</v>
+      </c>
+      <c r="E61" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="F61" s="19">
+        <v>65</v>
+      </c>
+      <c r="G61" s="19">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A62" s="46"/>
+      <c r="B62" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="C62" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="D62" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="E62" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="F62" s="19">
+        <v>75</v>
+      </c>
+      <c r="G62" s="19">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A63" s="46"/>
+      <c r="B63" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="C63" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="D63" s="16" t="s">
+        <v>546</v>
+      </c>
+      <c r="E63" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="F63" s="19">
+        <v>75</v>
+      </c>
+      <c r="G63" s="19">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A64" s="46"/>
+      <c r="B64" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="C64" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="D64" s="16" t="s">
+        <v>548</v>
+      </c>
+      <c r="E64" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="F64" s="19">
+        <v>60</v>
+      </c>
+      <c r="G64" s="19">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A65" s="46"/>
+      <c r="B65" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="C65" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="D65" s="16" t="s">
+        <v>550</v>
+      </c>
+      <c r="E65" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="F65" s="19">
+        <v>30</v>
+      </c>
+      <c r="G65" s="57">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A66" s="46" t="s">
+        <v>551</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="C66" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="D66" s="16" t="s">
+        <v>553</v>
+      </c>
+      <c r="E66" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="F66" s="53">
+        <v>55</v>
+      </c>
+      <c r="G66" s="53">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A67" s="46"/>
+      <c r="B67" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="C67" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="D67" s="16" t="s">
+        <v>555</v>
+      </c>
+      <c r="E67" s="19" t="s">
+        <v>502</v>
+      </c>
+      <c r="F67" s="53">
+        <v>100</v>
+      </c>
+      <c r="G67" s="1"/>
+    </row>
+    <row r="68" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A68" s="46"/>
+      <c r="B68" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="C68" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="D68" s="16" t="s">
+        <v>557</v>
+      </c>
+      <c r="E68" s="19" t="s">
+        <v>502</v>
+      </c>
+      <c r="F68" s="53">
+        <v>90</v>
+      </c>
+      <c r="G68" s="1"/>
+    </row>
+    <row r="69" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A69" s="46" t="s">
+        <v>558</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="C69" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D69" s="16" t="s">
+        <v>560</v>
+      </c>
+      <c r="E69" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="F69" s="53">
+        <v>60</v>
+      </c>
+      <c r="G69" s="53">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A70" s="46"/>
+      <c r="B70" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="C70" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="D70" s="16" t="s">
+        <v>562</v>
+      </c>
+      <c r="E70" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="F70" s="53">
+        <v>65</v>
+      </c>
+      <c r="G70" s="56">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A71" s="46"/>
+      <c r="B71" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="C71" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="D71" s="16" t="s">
+        <v>564</v>
+      </c>
+      <c r="E71" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="F71" s="53">
+        <v>65</v>
+      </c>
+      <c r="G71" s="56">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A72" s="46"/>
+      <c r="B72" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="C72" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="D72" s="16" t="s">
+        <v>566</v>
+      </c>
+      <c r="E72" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="F72" s="53">
+        <v>65</v>
+      </c>
+      <c r="G72" s="56">
+        <v>70</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A41:A65"/>
+    <mergeCell ref="A66:A68"/>
+    <mergeCell ref="A69:A72"/>
+    <mergeCell ref="A1:A6"/>
+    <mergeCell ref="A7:A14"/>
+    <mergeCell ref="A15:A26"/>
+    <mergeCell ref="A30:A32"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="A35:A40"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>